--- a/docs/MACRO STOCK CONTROL BODEGA.xlsx
+++ b/docs/MACRO STOCK CONTROL BODEGA.xlsx
@@ -8,15 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jazielove/Documents/GitHub/BodeGasosur/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9F625A-3CCB-554D-B4AE-18C1D973E2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11996AB9-E232-774E-9F3E-8347A7D3443E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INV. MAGALLANES" sheetId="1" r:id="rId1"/>
     <sheet name="INV. SERVI FER" sheetId="2" r:id="rId2"/>
     <sheet name="CATALOGO PROVEDORES" sheetId="3" r:id="rId3"/>
+    <sheet name="REFACCIONES" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">REFACCIONES!$A$7:$M$86</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -41,30 +45,21 @@
     <author>Compras Diana</author>
   </authors>
   <commentList>
-    <comment ref="B26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="B26" authorId="0" shapeId="0" xr:uid="{02183504-5C16-CD48-B9CF-6E709FDA91A0}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
-            <color rgb="FF000000"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>cotizar 3 juegos</t>
+cotizar 3 juegos</t>
         </r>
       </text>
     </comment>
-    <comment ref="M30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="M30" authorId="0" shapeId="0" xr:uid="{2E88C62C-3402-EA49-9784-26210E4EB299}">
       <text>
         <r>
           <rPr>
@@ -88,7 +83,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="M31" authorId="0" shapeId="0" xr:uid="{D2786AEF-2E05-9F40-A2FF-325680552D9E}">
       <text>
         <r>
           <rPr>
@@ -112,7 +107,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M43" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="M43" authorId="1" shapeId="0" xr:uid="{F703148B-55BB-824B-BDE1-B21B7EE9B571}">
       <text>
         <r>
           <rPr>
@@ -126,7 +121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H101" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="H101" authorId="1" shapeId="0" xr:uid="{E0E96D37-F620-A647-9CC7-167FE1388B6A}">
       <text>
         <r>
           <rPr>
@@ -140,7 +135,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J102" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="J102" authorId="1" shapeId="0" xr:uid="{3BF6FBF2-1F1D-EA42-A795-DE1E7EB4870D}">
       <text>
         <r>
           <rPr>
@@ -154,7 +149,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H103" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="H103" authorId="0" shapeId="0" xr:uid="{4A328FD0-653C-514A-8FD2-155786D41218}">
       <text>
         <r>
           <rPr>
@@ -168,7 +163,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H104" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="H104" authorId="0" shapeId="0" xr:uid="{9CEF4016-EF3D-FC47-B184-455967E0A4C7}">
       <text>
         <r>
           <rPr>
@@ -182,7 +177,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H105" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="H105" authorId="0" shapeId="0" xr:uid="{448585F2-543B-6F45-9802-C30D96E3AB86}">
       <text>
         <r>
           <rPr>
@@ -206,7 +201,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H106" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+    <comment ref="H106" authorId="0" shapeId="0" xr:uid="{C858304A-4291-0E46-B681-AEFBD01A98EA}">
       <text>
         <r>
           <rPr>
@@ -230,7 +225,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H107" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+    <comment ref="H107" authorId="1" shapeId="0" xr:uid="{02D849C0-2C25-9840-A1D3-3522BF1DF66A}">
       <text>
         <r>
           <rPr>
@@ -254,7 +249,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H108" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
+    <comment ref="H108" authorId="1" shapeId="0" xr:uid="{95A46994-90EB-904B-9631-2129DC363975}">
       <text>
         <r>
           <rPr>
@@ -278,7 +273,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H110" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
+    <comment ref="H110" authorId="1" shapeId="0" xr:uid="{9AD2A426-38F4-B843-AB59-053671331BD9}">
       <text>
         <r>
           <rPr>
@@ -303,53 +298,35 @@
         </r>
       </text>
     </comment>
-    <comment ref="B117" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
+    <comment ref="B117" authorId="1" shapeId="0" xr:uid="{0A644059-70F3-F64D-9CE5-29035C2DC842}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
-            <color rgb="FF000000"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>USAN DIAMANTE Y COPA</t>
+USAN DIAMANTE Y COPA</t>
         </r>
       </text>
     </comment>
-    <comment ref="B119" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
+    <comment ref="B119" authorId="1" shapeId="0" xr:uid="{9C88E2FB-0588-594D-AA3D-975877996EC5}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
-            <color rgb="FF000000"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve"> 
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>LIBERTADORES</t>
+LIBERTADORES</t>
         </r>
       </text>
     </comment>
-    <comment ref="P132" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
+    <comment ref="P132" authorId="1" shapeId="0" xr:uid="{6CC0BA4D-95C8-334F-9AEB-F92AB84B8A8E}">
       <text>
         <r>
           <rPr>
@@ -363,7 +340,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H140" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
+    <comment ref="H140" authorId="1" shapeId="0" xr:uid="{C493041E-E03C-2E4A-8A34-01DFCEBBD06A}">
       <text>
         <r>
           <rPr>
@@ -377,7 +354,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H141" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
+    <comment ref="H141" authorId="1" shapeId="0" xr:uid="{36ECC071-0A18-C045-976E-D7761C4944EC}">
       <text>
         <r>
           <rPr>
@@ -391,7 +368,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H145" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013000000}">
+    <comment ref="H145" authorId="1" shapeId="0" xr:uid="{5B233510-3076-BE40-AAA6-B32C88D1DFC5}">
       <text>
         <r>
           <rPr>
@@ -416,7 +393,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H146" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014000000}">
+    <comment ref="H146" authorId="1" shapeId="0" xr:uid="{784D8B03-E1E5-704C-9085-16B152178D5B}">
       <text>
         <r>
           <rPr>
@@ -441,7 +418,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H147" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000015000000}">
+    <comment ref="H147" authorId="1" shapeId="0" xr:uid="{ACAF01FE-CBD3-EF41-AC1C-7DE528CCA11F}">
       <text>
         <r>
           <rPr>
@@ -466,7 +443,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H148" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000016000000}">
+    <comment ref="H148" authorId="1" shapeId="0" xr:uid="{01A5ED03-F206-FD41-A2E5-EF06E6916541}">
       <text>
         <r>
           <rPr>
@@ -491,7 +468,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H149" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000017000000}">
+    <comment ref="H149" authorId="1" shapeId="0" xr:uid="{7FBED9B0-2802-8749-B0AA-28191F220EBE}">
       <text>
         <r>
           <rPr>
@@ -516,7 +493,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H150" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000018000000}">
+    <comment ref="H150" authorId="1" shapeId="0" xr:uid="{6B76713F-0A6B-9546-B2FC-2CA5865529E2}">
       <text>
         <r>
           <rPr>
@@ -541,7 +518,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H151" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000019000000}">
+    <comment ref="H151" authorId="1" shapeId="0" xr:uid="{9254572C-0735-7D4C-B9F9-EE0D3D4DC3C3}">
       <text>
         <r>
           <rPr>
@@ -566,7 +543,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H152" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001A000000}">
+    <comment ref="H152" authorId="1" shapeId="0" xr:uid="{7AE95361-1534-2444-9497-AB773F59C636}">
       <text>
         <r>
           <rPr>
@@ -591,13 +568,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="H153" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001B000000}">
+    <comment ref="H153" authorId="1" shapeId="0" xr:uid="{3ED62938-A767-0944-8432-21036FD2AC9B}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
-            <color rgb="FF000000"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -606,26 +583,17 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color rgb="FF000000"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">se compro en atm
+se compro en atm
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="H154" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001C000000}">
+    <comment ref="H154" authorId="1" shapeId="0" xr:uid="{A10072C7-A39A-7C47-AAF6-D10A0B2E04AF}">
       <text>
         <r>
           <rPr>
@@ -650,7 +618,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H155" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001D000000}">
+    <comment ref="H155" authorId="1" shapeId="0" xr:uid="{DEF5E01C-4B11-4443-ABCF-88BD4A388564}">
       <text>
         <r>
           <rPr>
@@ -773,7 +741,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2014" uniqueCount="903">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2409" uniqueCount="1057">
   <si>
     <t>CODIGO</t>
   </si>
@@ -3482,13 +3450,879 @@
   </si>
   <si>
     <t>RECEP. CAYACO 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obligatorio </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opcional </t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Clave producto SAT es el código del catálogo de producto del SAT </t>
+  </si>
+  <si>
+    <t>**Moneda es el código del catálogo de monedas del SAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clave producto SAT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SKU </t>
+  </si>
+  <si>
+    <t>Moneda</t>
+  </si>
+  <si>
+    <t>Unidad</t>
+  </si>
+  <si>
+    <t>Precio Unitario</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Tasa IVA tras</t>
+  </si>
+  <si>
+    <t>Tasa IVA ret</t>
+  </si>
+  <si>
+    <t>Tasa IEPS tras</t>
+  </si>
+  <si>
+    <t>Tasa IEPS ret</t>
+  </si>
+  <si>
+    <t>Tasa ISR</t>
+  </si>
+  <si>
+    <t>Factor</t>
+  </si>
+  <si>
+    <t>Año</t>
+  </si>
+  <si>
+    <t>´00004</t>
+  </si>
+  <si>
+    <t>MXN/USD</t>
+  </si>
+  <si>
+    <t>H87</t>
+  </si>
+  <si>
+    <t>PISTOLA DIESEL 1"</t>
+  </si>
+  <si>
+    <t>27112900</t>
+  </si>
+  <si>
+    <t>´00005</t>
+  </si>
+  <si>
+    <t>PISTOLA GASOLINA 3/4"</t>
+  </si>
+  <si>
+    <t>´00006</t>
+  </si>
+  <si>
+    <t>CALIBRADORES P/ AGUA Y AIRE</t>
+  </si>
+  <si>
+    <t>´00007</t>
+  </si>
+  <si>
+    <t>MANGUERAS VERDES AGUA Y AIRE</t>
+  </si>
+  <si>
+    <t>´00008</t>
+  </si>
+  <si>
+    <t>MANGUERAS AZULES AGUA Y AIRE</t>
+  </si>
+  <si>
+    <t>´00009</t>
+  </si>
+  <si>
+    <r>
+      <t>TRAMOS CORTOS DE 1" /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> MANGUERA PICTAIL NEGRO 1 X 12"</t>
+    </r>
+  </si>
+  <si>
+    <t>´00010</t>
+  </si>
+  <si>
+    <t>´00011</t>
+  </si>
+  <si>
+    <t>´00012</t>
+  </si>
+  <si>
+    <t>VALVULAS DE CORTE DE 3/4 GASOLINA</t>
+  </si>
+  <si>
+    <t>´00013</t>
+  </si>
+  <si>
+    <t>ADAPTADORES DE BRONCE DE 4"</t>
+  </si>
+  <si>
+    <t>´00014</t>
+  </si>
+  <si>
+    <t>´00015</t>
+  </si>
+  <si>
+    <t>´00016</t>
+  </si>
+  <si>
+    <t>´00017</t>
+  </si>
+  <si>
+    <t>´00018</t>
+  </si>
+  <si>
+    <t>´00019</t>
+  </si>
+  <si>
+    <t>FILTRO DIESEL 30 MICRAS DE 1 PULGADA PETROCLEAR (CM TEK 70016)</t>
+  </si>
+  <si>
+    <t>´00020</t>
+  </si>
+  <si>
+    <t>´00021</t>
+  </si>
+  <si>
+    <r>
+      <t>VALVULAS SHUT-OFF (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> OPW 1.5 SENCILLA)</t>
+    </r>
+  </si>
+  <si>
+    <t>´00022</t>
+  </si>
+  <si>
+    <t>´00023</t>
+  </si>
+  <si>
+    <t>´00024</t>
+  </si>
+  <si>
+    <r>
+      <t>TARJETA DE MODULO DE PROBETA PARA VEEDER-ROOT / T</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ARJETA VEEDER ROOT #329356-002 MODULO DE PROBETA</t>
+    </r>
+  </si>
+  <si>
+    <t>´00025</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FUENTE DE PODER BENNET / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TARJETA BENNETT # 131219S FUENTE DE PODER</t>
+    </r>
+  </si>
+  <si>
+    <t>´00026</t>
+  </si>
+  <si>
+    <t>´00027</t>
+  </si>
+  <si>
+    <t>´00028</t>
+  </si>
+  <si>
+    <r>
+      <t>VALVULA SKINER 24 VOLTS ALTO FLUJO /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> BENNETT VALVULA SKINNER DIESEL 1 1/2 " 24VDC C/BRIDA #114606</t>
+    </r>
+  </si>
+  <si>
+    <t>´00029</t>
+  </si>
+  <si>
+    <t>´00030</t>
+  </si>
+  <si>
+    <r>
+      <t>ARRESTA FLAMA DIESEL OPW</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / OPW VALVULA ARRESTADOR DE FLAMA 2" 515ML-1030</t>
+    </r>
+  </si>
+  <si>
+    <t>´00031</t>
+  </si>
+  <si>
+    <r>
+      <t>KIT DE FLOTADORES P/GASOLINA /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>VEEDER ROOT KIT DE FLOTADOR P/GASOLINA 846402-000-CABLE 5"</t>
+    </r>
+  </si>
+  <si>
+    <t>´00032</t>
+  </si>
+  <si>
+    <t>GASOILIA / GASOILA 1 PINTA SS16</t>
+  </si>
+  <si>
+    <t>´00033</t>
+  </si>
+  <si>
+    <t>´00034</t>
+  </si>
+  <si>
+    <t>´00035</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">EPOXICO </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/ FIBRA DE VIDRIO KIT DE PEGAMENTO  6 OZ</t>
+    </r>
+  </si>
+  <si>
+    <t>´00036</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">MODULO RS232PARA VEEDER </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TARJETA  GR-1000 DE COMUNICACION P/ VEDDER ROOT</t>
+    </r>
+  </si>
+  <si>
+    <t>´00037</t>
+  </si>
+  <si>
+    <r>
+      <t>MICRO SWITCH /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> TARJETA BENNETT #111171S MICROSWITCH</t>
+    </r>
+  </si>
+  <si>
+    <t>´00038</t>
+  </si>
+  <si>
+    <t>´00039</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FUSIBLE O PATITA DE SHUT-OFF </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OPW ELEMENTO (BRAZO) PARA VALUVULA SHUT OFF H05361</t>
+    </r>
+  </si>
+  <si>
+    <t>´00040</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SHUT P/AIRE DE DIESEL / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CHUCK DE  AIRE 1/4 SCH-200 / 250 V</t>
+    </r>
+  </si>
+  <si>
+    <t>´00041</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">VALVULAS P/AIRE MOD. ANTERIOR / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PISTOLA DE AIRE MCA. AMFLO MOD. 150</t>
+    </r>
+  </si>
+  <si>
+    <t>´00042</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">PISTOLAS P/AGUA NEGRA </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/PISTOLA DE AGUA MCA. AMFLO MOD. 40R</t>
+    </r>
+  </si>
+  <si>
+    <t>´00043</t>
+  </si>
+  <si>
+    <t>´00044</t>
+  </si>
+  <si>
+    <t>´00045</t>
+  </si>
+  <si>
+    <t>´00046</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">RESORDE P/PALANCA </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/ BENNETT RESORTE P/RECEPTACULO HORIZON #J696601</t>
+    </r>
+  </si>
+  <si>
+    <t>´00047</t>
+  </si>
+  <si>
+    <r>
+      <t>CABLES DE COMUNICACIÓN P/PROBETA VEEDER ROOT /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> VEEDER ROOT  CABLES P/PROBETA 10 FT #330272-002</t>
+    </r>
+  </si>
+  <si>
+    <t>´00048</t>
+  </si>
+  <si>
+    <r>
+      <t>CARTUCHO DE 1.5 HP /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> RED JACKET MOTOR P/TURBINA 1.5HP UMP150U1 208/230 RJ-852-200</t>
+    </r>
+  </si>
+  <si>
+    <t>´00049</t>
+  </si>
+  <si>
+    <r>
+      <t>VALVULAS SKINER DE DIESEL DE 2 HILOS CURVA /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> BENNETT VALVULA SKINNER ATLANTIC 1 # 137695</t>
+    </r>
+  </si>
+  <si>
+    <t>´00050</t>
+  </si>
+  <si>
+    <t>´00051</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">VALVUAS WAYNE SKINER / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>WAYNE VALVULA SELENOIDE W2893703-001</t>
+    </r>
+  </si>
+  <si>
+    <t>´00052</t>
+  </si>
+  <si>
+    <t>´00053</t>
+  </si>
+  <si>
+    <t>´00054</t>
+  </si>
+  <si>
+    <t>´00055</t>
+  </si>
+  <si>
+    <t>CONTENEDOR DE DERRAMES DE DOBLE PARED</t>
+  </si>
+  <si>
+    <t>´00056</t>
+  </si>
+  <si>
+    <t>´00057</t>
+  </si>
+  <si>
+    <t>´00058</t>
+  </si>
+  <si>
+    <t>FUNDAS PISTOLA VERDE / OPW</t>
+  </si>
+  <si>
+    <t>´00059</t>
+  </si>
+  <si>
+    <t>FUNDAS PISTOLA ROJA / OPW</t>
+  </si>
+  <si>
+    <t>´00060</t>
+  </si>
+  <si>
+    <t>FUNDAS NEGRAS 1" / OPW</t>
+  </si>
+  <si>
+    <t>´00061</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">MANGUERAS DE DIESEL / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">MANGUERA DE DIESEL 1" X 20 FT NEGRA GIRATORIA </t>
+    </r>
+  </si>
+  <si>
+    <t>´00062</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">MANGUERAS DE GASOLINA / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">MANGUERA DE GASOLINA 3/4 X 12 FT NEGRA GIRATORIA </t>
+    </r>
+  </si>
+  <si>
+    <t>´00063</t>
+  </si>
+  <si>
+    <r>
+      <t>BOTA FLEXIBLE 1 PULGADA A 3/4 /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> BOTA BIPARTIDA 1 - 3/4</t>
+    </r>
+  </si>
+  <si>
+    <t>´00064</t>
+  </si>
+  <si>
+    <t>BOTA FLEXIBLE 2 PULGADA</t>
+  </si>
+  <si>
+    <t>´00065</t>
+  </si>
+  <si>
+    <t>BOTA FLEXIBLE 4 PULGADA 1 1/2</t>
+  </si>
+  <si>
+    <t>´00066</t>
+  </si>
+  <si>
+    <t>´00067</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FILTRO DE ALTO FLUJO DIESEL WAYNE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/ FILTRO P/DISP. 70016 CIMTEK 30 MICRONES 1</t>
+    </r>
+  </si>
+  <si>
+    <t>´00068</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FILTRO GASOLINA BENNET 10 MICRAS / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FILTRO P/DISP. 70010 CIMTEK 10 MICRONES 3/4</t>
+    </r>
+  </si>
+  <si>
+    <t>´00069</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FILTRO GASOLINA BENNET 30 MICRAS / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FILTRO P/DISP. 70012 CIMTEK 30 MICRONES 3/4</t>
+    </r>
+  </si>
+  <si>
+    <t>´00070</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FILTRO GASOLINA WAYNE 10 MICRAS / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> FILTRO P/DISP. 70015 CIMTEK 30 MICRONES 3/4</t>
+    </r>
+  </si>
+  <si>
+    <t>´00071</t>
+  </si>
+  <si>
+    <t>´00072</t>
+  </si>
+  <si>
+    <t>´00073</t>
+  </si>
+  <si>
+    <t>MANGUERAS DE DESCARGA</t>
+  </si>
+  <si>
+    <t>´00074</t>
+  </si>
+  <si>
+    <t>COPLE ELECTRICO DE 3/4 X 18</t>
+  </si>
+  <si>
+    <t>´00075</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">COPLE ELECTRICO DE 3/4 X 21 / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MANGUERA FLEXIBLE 3/4 X 24" MX COPLEFLEX</t>
+    </r>
+  </si>
+  <si>
+    <t>´00076</t>
+  </si>
+  <si>
+    <t>´00077</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">REGISTROS OPW 12 PULGADAS / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OPW REGISTRO 12" 104A-1200</t>
+    </r>
+  </si>
+  <si>
+    <t>´00078</t>
+  </si>
+  <si>
+    <r>
+      <t>CONSOLAS VEDEER ROOT /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> VEEDER ROOT CONSOLA TLS450C/IMPRESORA # 0860091-302</t>
+    </r>
+  </si>
+  <si>
+    <t>´00079</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">DISPENSARIOS DE AGUA Y AIRE COMPLETO / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DISPENSARIO PARA  AGUA/AIRE IMAGEN PEMEX</t>
+    </r>
+  </si>
+  <si>
+    <t>´00080</t>
+  </si>
+  <si>
+    <t>VALVULA DE VENTEO OPW 3 A 2 / EMCO WHEATON VALVULA DE VENTEO # A0084-105</t>
+  </si>
+  <si>
+    <t>´00081</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">VALVULA DE RECUPERACION DE VAPORES / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OPW ADAPTADOR P/RECU. DE VAPORES 4" 1611AV-1620</t>
+    </r>
+  </si>
+  <si>
+    <t>´00082</t>
+  </si>
+  <si>
+    <t>**Unidad H87 es Pieza</t>
+  </si>
+  <si>
+    <t>CAPACITOR EMIGDIO</t>
+  </si>
+  <si>
+    <t>CAPACITOR DON PONCHO</t>
+  </si>
+  <si>
+    <t>TRAMO CORTO DE 3/4"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMIGDIO </t>
+  </si>
+  <si>
+    <t>EMIGDIO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3530,20 +4364,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3562,8 +4406,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -3571,11 +4433,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3598,11 +4475,39 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="13">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -3677,24 +4582,6 @@
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3876,6 +4763,213 @@
         <a:xfrm>
           <a:off x="12732124" y="724796"/>
           <a:ext cx="8926605" cy="480509"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="es-MX" sz="2800" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SALIDAS</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>744070</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="3 Rectángulo redondeado">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DEE1E93-A790-594B-B33D-3EB36CE093E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="22860" y="627380"/>
+          <a:ext cx="7668110" cy="518160"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="es-MX" sz="2800" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>PRODUCTOS</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>8966</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>779929</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="4 Rectángulo redondeado">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9980EC5-EE65-4C43-8AF6-8D457221F7CF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7933766" y="627380"/>
+          <a:ext cx="6320863" cy="563880"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="es-MX" sz="2800" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ENTRADAS</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>860611</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="5 Rectángulo redondeado">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE7938FE-A1D2-DD4E-92E4-FE89A81CE9C6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14554200" y="604520"/>
+          <a:ext cx="11325411" cy="502920"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -4134,19 +5228,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PRODUCTOS" displayName="PRODUCTOS" ref="A8:E143" totalsRowShown="0">
-  <autoFilter ref="A8:E143" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{3BB68E16-2A7D-C34F-8F47-E7277598F909}" name="PRODUCTOS9" displayName="PRODUCTOS9" ref="A8:E145" totalsRowShown="0">
+  <autoFilter ref="A8:E145" xr:uid="{3BB68E16-2A7D-C34F-8F47-E7277598F909}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="CODIGO"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ARTICULO"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ENTRADAS" dataDxfId="12">
-      <calculatedColumnFormula>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{B0F0A01F-84AB-6E43-B800-3DCCAE4688AB}" name="CODIGO"/>
+    <tableColumn id="2" xr3:uid="{453D69FD-7A82-DB46-B2BC-431C7EF92442}" name="ARTICULO"/>
+    <tableColumn id="3" xr3:uid="{048679B8-571D-F840-AE9B-C9BF29D0885A}" name="ENTRADAS" dataDxfId="4">
+      <calculatedColumnFormula>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="SALIDAS" dataDxfId="11">
-      <calculatedColumnFormula>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</calculatedColumnFormula>
+    <tableColumn id="4" xr3:uid="{9F9DA9B8-8021-8743-8873-930F2E74236A}" name="SALIDAS" dataDxfId="3">
+      <calculatedColumnFormula>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="STOCK" dataDxfId="10">
-      <calculatedColumnFormula>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</calculatedColumnFormula>
+    <tableColumn id="5" xr3:uid="{809881AF-AA14-034C-ABFC-B0DA3461D895}" name="STOCK" dataDxfId="2">
+      <calculatedColumnFormula>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium28" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4154,52 +5248,52 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="ENTRADAS" displayName="ENTRADAS" ref="G8:J166" totalsRowShown="0">
-  <autoFilter ref="G8:J166" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{10683C36-51A1-594A-A783-F1DDA5B3F996}" name="ENTRADAS10" displayName="ENTRADAS10" ref="G8:J165" totalsRowShown="0">
+  <autoFilter ref="G8:J165" xr:uid="{10683C36-51A1-594A-A783-F1DDA5B3F996}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="CODIGO"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="ARTICULO">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{9390FC2A-0C2C-4849-8980-609EBB4F5A68}" name="CODIGO"/>
+    <tableColumn id="2" xr3:uid="{DCE33E22-8FB6-6945-8CC0-7DF8A38B74A1}" name="ARTICULO">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="FECHA"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="CANTIDAD" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{E139BCA5-3A46-1C4E-8B9C-4D9900FA837B}" name="FECHA"/>
+    <tableColumn id="4" xr3:uid="{6B4E1C47-47DE-1745-A8DF-FD16DFFC0D4A}" name="CANTIDAD" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium25" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="SALIDAS" displayName="SALIDAS" ref="L8:S141" totalsRowShown="0">
-  <autoFilter ref="L8:S141" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{7F726405-4F6E-D44F-9E6E-DE7336F0B6BA}" name="SALIDAS11" displayName="SALIDAS11" ref="L8:S150" totalsRowShown="0">
+  <autoFilter ref="L8:S150" xr:uid="{7F726405-4F6E-D44F-9E6E-DE7336F0B6BA}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="CODIGO"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="ARTICULO">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{62EA7372-94B9-AB49-A486-C6A902A3621F}" name="CODIGO"/>
+    <tableColumn id="2" xr3:uid="{58A7A0C1-03FB-4344-AB5B-67190650C2EB}" name="ARTICULO">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="FECHA"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="CANTIDAD" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="ESTACION"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="QUIEN SE LO LLEVA"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="DIAGNOSTICO"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="AUTORIZO"/>
+    <tableColumn id="3" xr3:uid="{DFC85145-C859-5E45-88C9-28615BECF38D}" name="FECHA"/>
+    <tableColumn id="4" xr3:uid="{2674A14A-E884-7948-A426-6722492EBEBD}" name="CANTIDAD" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{F66C788A-1EA0-6D49-A487-C4F6899F1D17}" name="ESTACION"/>
+    <tableColumn id="6" xr3:uid="{0D037146-A7DE-9841-A7FD-C4D0C559FC41}" name="QUIEN SE LO LLEVA"/>
+    <tableColumn id="7" xr3:uid="{B0DE5A25-899F-774F-B2B1-6300DB66D53D}" name="DIAGNOSTICO"/>
+    <tableColumn id="8" xr3:uid="{0B503D7A-F4F9-D344-B10D-2626685DA817}" name="AUTORIZO"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium26" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="PRODUCTOS5" displayName="PRODUCTOS5" ref="A8:E116" totalsRowShown="0" headerRowDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="PRODUCTOS5" displayName="PRODUCTOS5" ref="A8:E116" totalsRowShown="0" headerRowDxfId="12">
   <autoFilter ref="A8:E116" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="CODIGO"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="ARTICULO"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="ENTRADAS" dataDxfId="6">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="ENTRADAS" dataDxfId="11">
       <calculatedColumnFormula>SUMIF(ENTRADAS6[CODIGO],PRODUCTOS5[[#This Row],[CODIGO]],ENTRADAS6[CANTIDAD])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="SALIDAS" dataDxfId="5">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="SALIDAS" dataDxfId="10">
       <calculatedColumnFormula>SUMIF(SALIDAS7[CODIGO],PRODUCTOS5[[#This Row],[CODIGO]],SALIDAS7[CANTIDAD])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="STOCK" dataDxfId="4">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="STOCK" dataDxfId="9">
       <calculatedColumnFormula>PRODUCTOS5[[#This Row],[ENTRADAS]]-PRODUCTOS5[[#This Row],[SALIDAS]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4208,7 +5302,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="ENTRADAS6" displayName="ENTRADAS6" ref="G8:J116" totalsRowShown="0" headerRowDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="ENTRADAS6" displayName="ENTRADAS6" ref="G8:J116" totalsRowShown="0" headerRowDxfId="8">
   <autoFilter ref="G8:J116" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="CODIGO"/>
@@ -4216,14 +5310,14 @@
       <calculatedColumnFormula>IFERROR(VLOOKUP(ENTRADAS6[[#This Row],[CODIGO]],PRODUCTOS5[],2,FALSE),"NO EXISTE")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="FECHA"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="CANTIDAD" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="CANTIDAD" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium25" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="SALIDAS7" displayName="SALIDAS7" ref="L8:S30" totalsRowShown="0" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="SALIDAS7" displayName="SALIDAS7" ref="L8:S30" totalsRowShown="0" headerRowDxfId="6">
   <autoFilter ref="L8:S30" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="CODIGO"/>
@@ -4231,7 +5325,7 @@
       <calculatedColumnFormula>IFERROR(VLOOKUP(SALIDAS7[[#This Row],[CODIGO]],PRODUCTOS5[],2,FALSE),"NO EXISTE")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="FECHA"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="CANTIDAD" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="CANTIDAD" dataDxfId="5"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="ESTACION"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="QUIEN SE LO LLEVA"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="AUTORIZO "/>
@@ -4544,9 +5638,31 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{FC7794A9-FE19-C149-BE38-945DB401CF03}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="es-ES" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;d0f0e597-855b-45dd-b7fd-6a3f754c6bc8&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S166"/>
+  <dimension ref="A1:S165"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="52.5" bestFit="1" customWidth="1"/>
@@ -4713,22 +5829,22 @@
         <v>7</v>
       </c>
       <c r="C9" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>11</v>
       </c>
       <c r="D9" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>7</v>
       </c>
       <c r="E9" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>4</v>
       </c>
       <c r="G9" t="s">
         <v>96</v>
       </c>
       <c r="H9" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CALIBRADORES GRIPPER A/A</v>
       </c>
       <c r="I9" s="2">
@@ -4741,7 +5857,7 @@
         <v>153</v>
       </c>
       <c r="M9" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>TITIFLEX 1 1/2 X 24 PULGADAS</v>
       </c>
       <c r="N9" s="2">
@@ -4771,22 +5887,22 @@
         <v>8</v>
       </c>
       <c r="C10" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>108</v>
       </c>
       <c r="D10" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
-        <v>33</v>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
+        <v>34</v>
       </c>
       <c r="E10" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
-        <v>75</v>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
+        <v>74</v>
       </c>
       <c r="G10" t="s">
         <v>97</v>
       </c>
       <c r="H10" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERAS VERDES A/A</v>
       </c>
       <c r="I10" s="2">
@@ -4799,7 +5915,7 @@
         <v>105</v>
       </c>
       <c r="M10" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PULSADORES P/ DISPENSARIO BENNET</v>
       </c>
       <c r="N10" s="2">
@@ -4829,22 +5945,22 @@
         <v>9</v>
       </c>
       <c r="C11" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>14</v>
       </c>
       <c r="D11" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>14</v>
       </c>
       <c r="E11" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>0</v>
       </c>
       <c r="G11" t="s">
         <v>98</v>
       </c>
       <c r="H11" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERAS AZULES A/A</v>
       </c>
       <c r="I11" s="2">
@@ -4857,7 +5973,7 @@
         <v>105</v>
       </c>
       <c r="M11" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PULSADORES P/ DISPENSARIO BENNET</v>
       </c>
       <c r="N11" s="2">
@@ -4887,22 +6003,22 @@
         <v>10</v>
       </c>
       <c r="C12" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>4</v>
       </c>
       <c r="D12" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E12" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>4</v>
       </c>
       <c r="G12" t="s">
         <v>99</v>
       </c>
       <c r="H12" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>TRAMOS CORTOS DE 1"</v>
       </c>
       <c r="I12" s="2">
@@ -4915,7 +6031,7 @@
         <v>143</v>
       </c>
       <c r="M12" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CABLES DE COMUNICACIÓN P/PROVETA VEEDER ROOT</v>
       </c>
       <c r="N12" s="2">
@@ -4945,22 +6061,22 @@
         <v>11</v>
       </c>
       <c r="C13" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>57</v>
       </c>
       <c r="D13" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
-        <v>17</v>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
+        <v>21</v>
       </c>
       <c r="E13" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
-        <v>40</v>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
+        <v>36</v>
       </c>
       <c r="G13" t="s">
         <v>100</v>
       </c>
       <c r="H13" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PISTOLA DE 3/4 P/GASOLINA</v>
       </c>
       <c r="I13" s="2">
@@ -4973,7 +6089,7 @@
         <v>169</v>
       </c>
       <c r="M13" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>DESTORCEDORES 3/4 GASOLINA OPW</v>
       </c>
       <c r="N13" s="2">
@@ -5003,22 +6119,22 @@
         <v>12</v>
       </c>
       <c r="C14" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>56</v>
       </c>
       <c r="D14" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>2</v>
       </c>
       <c r="E14" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>54</v>
       </c>
       <c r="G14" t="s">
         <v>101</v>
       </c>
       <c r="H14" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PISTOLA DE 1 PULGADA P/DIESEL</v>
       </c>
       <c r="I14" s="2">
@@ -5031,7 +6147,7 @@
         <v>100</v>
       </c>
       <c r="M14" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PISTOLA DE 3/4 P/GASOLINA</v>
       </c>
       <c r="N14" s="2">
@@ -5061,22 +6177,22 @@
         <v>13</v>
       </c>
       <c r="C15" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>3</v>
       </c>
       <c r="D15" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E15" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>3</v>
       </c>
       <c r="G15" t="s">
         <v>102</v>
       </c>
       <c r="H15" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>TARJETA DE DISPLAY WAYNE VOLUMEN</v>
       </c>
       <c r="I15" s="2">
@@ -5089,7 +6205,7 @@
         <v>117</v>
       </c>
       <c r="M15" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PALANCAS DE ACTIVACION PARA DIESEL WAYNE</v>
       </c>
       <c r="N15" s="2">
@@ -5119,22 +6235,22 @@
         <v>14</v>
       </c>
       <c r="C16" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>112</v>
       </c>
       <c r="D16" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E16" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>112</v>
       </c>
       <c r="G16" t="s">
         <v>103</v>
       </c>
       <c r="H16" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>BATERIAS DE 12 V P/DISPENSARIO BENNET</v>
       </c>
       <c r="I16" s="2">
@@ -5147,7 +6263,7 @@
         <v>187</v>
       </c>
       <c r="M16" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>SENSOR LIQUIDO DE BRONCE</v>
       </c>
       <c r="N16" s="2">
@@ -5177,22 +6293,22 @@
         <v>15</v>
       </c>
       <c r="C17" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>33</v>
       </c>
       <c r="D17" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E17" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>33</v>
       </c>
       <c r="G17" t="s">
         <v>104</v>
       </c>
       <c r="H17" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PALANCAS P/GASOLINA ATLANTIC BENNET</v>
       </c>
       <c r="I17" s="2">
@@ -5205,7 +6321,7 @@
         <v>187</v>
       </c>
       <c r="M17" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>SENSOR LIQUIDO DE BRONCE</v>
       </c>
       <c r="N17" s="2">
@@ -5235,22 +6351,22 @@
         <v>16</v>
       </c>
       <c r="C18" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>32</v>
       </c>
       <c r="D18" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>3</v>
       </c>
       <c r="E18" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>29</v>
       </c>
       <c r="G18" t="s">
         <v>105</v>
       </c>
       <c r="H18" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PULSADORES P/ DISPENSARIO BENNET</v>
       </c>
       <c r="I18" s="2">
@@ -5263,7 +6379,7 @@
         <v>187</v>
       </c>
       <c r="M18" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>SENSOR LIQUIDO DE BRONCE</v>
       </c>
       <c r="N18" s="2">
@@ -5293,22 +6409,22 @@
         <v>17</v>
       </c>
       <c r="C19" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D19" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E19" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>1</v>
       </c>
       <c r="G19" t="s">
         <v>106</v>
       </c>
       <c r="H19" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>DIAFRAGMA P/ VALVULA SKINNER</v>
       </c>
       <c r="I19" s="2">
@@ -5321,7 +6437,7 @@
         <v>146</v>
       </c>
       <c r="M19" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>SENSORES UNIVERSALES GRIS</v>
       </c>
       <c r="N19" s="2">
@@ -5351,22 +6467,22 @@
         <v>18</v>
       </c>
       <c r="C20" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>29</v>
       </c>
       <c r="D20" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E20" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>29</v>
       </c>
       <c r="G20" t="s">
         <v>107</v>
       </c>
       <c r="H20" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PALANCAS P/GASOLINA PACIFIC BENNET</v>
       </c>
       <c r="I20" s="2">
@@ -5379,7 +6495,7 @@
         <v>179</v>
       </c>
       <c r="M20" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>REGISTROS OPW 12 PULGADAS</v>
       </c>
       <c r="N20" s="2">
@@ -5409,22 +6525,22 @@
         <v>19</v>
       </c>
       <c r="C21" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>245</v>
       </c>
       <c r="D21" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="E21" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>244</v>
       </c>
       <c r="G21" t="s">
         <v>108</v>
       </c>
       <c r="H21" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>VALVULA DE CORTE DE 3/4 GASOLINA</v>
       </c>
       <c r="I21" s="2">
@@ -5437,7 +6553,7 @@
         <v>147</v>
       </c>
       <c r="M21" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>VALVULAS WAYNE SKINER HELIX W2893703-001</v>
       </c>
       <c r="N21" s="2">
@@ -5467,22 +6583,22 @@
         <v>20</v>
       </c>
       <c r="C22" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>3</v>
       </c>
       <c r="D22" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="E22" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>2</v>
       </c>
       <c r="G22" t="s">
         <v>109</v>
       </c>
       <c r="H22" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>ADAPTADORES DE BRONCE DE 4 PULGADAS</v>
       </c>
       <c r="I22" s="2">
@@ -5495,7 +6611,7 @@
         <v>96</v>
       </c>
       <c r="M22" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CALIBRADORES GRIPPER A/A</v>
       </c>
       <c r="N22" s="2">
@@ -5525,22 +6641,22 @@
         <v>21</v>
       </c>
       <c r="C23" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>36</v>
       </c>
       <c r="D23" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E23" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>36</v>
       </c>
       <c r="G23" t="s">
         <v>110</v>
       </c>
       <c r="H23" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>FILTRO DIESEL 30 MICRAS DE 1 PULGADA PETROCLEAR</v>
       </c>
       <c r="I23" s="2">
@@ -5553,7 +6669,7 @@
         <v>147</v>
       </c>
       <c r="M23" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>VALVULAS WAYNE SKINER HELIX W2893703-001</v>
       </c>
       <c r="N23" s="2">
@@ -5583,22 +6699,22 @@
         <v>22</v>
       </c>
       <c r="C24" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>12</v>
       </c>
       <c r="D24" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E24" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>12</v>
       </c>
       <c r="G24" t="s">
         <v>111</v>
       </c>
       <c r="H24" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>FILTRO GASOLINA 10 MICRAS DE 3/4 PULGADA PETROCLEAR</v>
       </c>
       <c r="I24" s="2">
@@ -5611,7 +6727,7 @@
         <v>100</v>
       </c>
       <c r="M24" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PISTOLA DE 3/4 P/GASOLINA</v>
       </c>
       <c r="N24" s="2">
@@ -5641,22 +6757,22 @@
         <v>23</v>
       </c>
       <c r="C25" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>15</v>
       </c>
       <c r="D25" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E25" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>15</v>
       </c>
       <c r="G25" t="s">
         <v>112</v>
       </c>
       <c r="H25" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>VALVULAS SHUT-OFF</v>
       </c>
       <c r="I25" s="2">
@@ -5669,7 +6785,7 @@
         <v>172</v>
       </c>
       <c r="M25" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>COMPRESOR HORIZONTAL (PRUEBAS)</v>
       </c>
       <c r="N25" s="2">
@@ -5699,22 +6815,22 @@
         <v>24</v>
       </c>
       <c r="C26" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>10</v>
       </c>
       <c r="D26" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>8</v>
       </c>
       <c r="E26" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>2</v>
       </c>
       <c r="G26" t="s">
         <v>113</v>
       </c>
       <c r="H26" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>RADIOS MAG ONE</v>
       </c>
       <c r="I26" s="2">
@@ -5727,7 +6843,7 @@
         <v>179</v>
       </c>
       <c r="M26" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>REGISTROS OPW 12 PULGADAS</v>
       </c>
       <c r="N26" s="2">
@@ -5757,22 +6873,22 @@
         <v>25</v>
       </c>
       <c r="C27" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>4</v>
       </c>
       <c r="D27" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E27" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>4</v>
       </c>
       <c r="G27" t="s">
         <v>114</v>
       </c>
       <c r="H27" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>VALVULA DE CORTE DE 1 PULGADA DIESEL</v>
       </c>
       <c r="I27" s="2">
@@ -5785,7 +6901,7 @@
         <v>187</v>
       </c>
       <c r="M27" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>SENSOR LIQUIDO DE BRONCE</v>
       </c>
       <c r="N27" s="2">
@@ -5815,22 +6931,22 @@
         <v>26</v>
       </c>
       <c r="C28" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D28" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E28" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>1</v>
       </c>
       <c r="G28" t="s">
         <v>115</v>
       </c>
       <c r="H28" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>TARJETA DE MODULO DE PROVETA PARA VEEDER-ROOT</v>
       </c>
       <c r="I28" s="2">
@@ -5843,7 +6959,7 @@
         <v>171</v>
       </c>
       <c r="M28" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CONTADORAS DE MONEDAS</v>
       </c>
       <c r="N28" s="2">
@@ -5873,22 +6989,22 @@
         <v>27</v>
       </c>
       <c r="C29" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D29" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E29" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>1</v>
       </c>
       <c r="G29" t="s">
         <v>116</v>
       </c>
       <c r="H29" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>FUENTE DE PODER BENNET</v>
       </c>
       <c r="I29" s="2">
@@ -5901,7 +7017,7 @@
         <v>288</v>
       </c>
       <c r="M29" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>TROMPA DE COCHINO CODO DE DESCARGA</v>
       </c>
       <c r="N29" s="2">
@@ -5931,22 +7047,22 @@
         <v>28</v>
       </c>
       <c r="C30" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>11</v>
       </c>
       <c r="D30" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
+        <v>6</v>
+      </c>
+      <c r="E30" s="8">
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>5</v>
-      </c>
-      <c r="E30" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
-        <v>6</v>
       </c>
       <c r="G30" t="s">
         <v>117</v>
       </c>
       <c r="H30" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PALANCAS DE ACTIVACION PARA DIESEL WAYNE</v>
       </c>
       <c r="I30" s="2">
@@ -5959,7 +7075,7 @@
         <v>96</v>
       </c>
       <c r="M30" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CALIBRADORES GRIPPER A/A</v>
       </c>
       <c r="N30" s="2">
@@ -5989,22 +7105,22 @@
         <v>29</v>
       </c>
       <c r="C31" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>69</v>
       </c>
       <c r="D31" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>4</v>
       </c>
       <c r="E31" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>65</v>
       </c>
       <c r="G31" t="s">
         <v>118</v>
       </c>
       <c r="H31" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>DESTORCEDOR DE DIESEL 1 PULGADA OPW CODO</v>
       </c>
       <c r="I31" s="2">
@@ -6017,7 +7133,7 @@
         <v>181</v>
       </c>
       <c r="M31" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">DISPENSARIOS DE AGUA Y AIRE </v>
       </c>
       <c r="N31" s="2">
@@ -6047,22 +7163,22 @@
         <v>30</v>
       </c>
       <c r="C32" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D32" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E32" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>1</v>
       </c>
       <c r="G32" t="s">
         <v>119</v>
       </c>
       <c r="H32" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>VALVULA SKINER 24 VOLTS ALTO FLUJO</v>
       </c>
       <c r="I32" s="2">
@@ -6075,7 +7191,7 @@
         <v>117</v>
       </c>
       <c r="M32" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PALANCAS DE ACTIVACION PARA DIESEL WAYNE</v>
       </c>
       <c r="N32" s="2">
@@ -6105,22 +7221,22 @@
         <v>31</v>
       </c>
       <c r="C33" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D33" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E33" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>1</v>
       </c>
       <c r="G33" t="s">
         <v>120</v>
       </c>
       <c r="H33" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>NIPLE GALVANIZADO DE 4 PULGADAS</v>
       </c>
       <c r="I33" s="2">
@@ -6133,7 +7249,7 @@
         <v>138</v>
       </c>
       <c r="M33" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PISTOLAS P/AGUA NEGRA</v>
       </c>
       <c r="N33" s="2">
@@ -6163,22 +7279,22 @@
         <v>32</v>
       </c>
       <c r="C34" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>2</v>
       </c>
       <c r="D34" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E34" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>2</v>
       </c>
       <c r="G34" t="s">
         <v>121</v>
       </c>
       <c r="H34" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>ARRESTA FLAMA DIESEL</v>
       </c>
       <c r="I34" s="2">
@@ -6191,7 +7307,7 @@
         <v>136</v>
       </c>
       <c r="M34" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>SHUT P/AIRE DE DIESEL</v>
       </c>
       <c r="N34" s="2">
@@ -6221,22 +7337,22 @@
         <v>33</v>
       </c>
       <c r="C35" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D35" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E35" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>1</v>
       </c>
       <c r="G35" t="s">
         <v>122</v>
       </c>
       <c r="H35" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>KIT DE FLOTADORES P/GASOLINA</v>
       </c>
       <c r="I35" s="2">
@@ -6249,7 +7365,7 @@
         <v>98</v>
       </c>
       <c r="M35" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERAS AZULES A/A</v>
       </c>
       <c r="N35" s="2">
@@ -6279,22 +7395,22 @@
         <v>34</v>
       </c>
       <c r="C36" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>6</v>
       </c>
       <c r="D36" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E36" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>6</v>
       </c>
       <c r="G36" t="s">
         <v>123</v>
       </c>
       <c r="H36" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>GASOILIA</v>
       </c>
       <c r="I36" s="2">
@@ -6307,7 +7423,7 @@
         <v>287</v>
       </c>
       <c r="M36" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>VALVULA SKINNER RECTA DE 2 HILOS 24V #135461 PACIFIC</v>
       </c>
       <c r="N36" s="2">
@@ -6337,22 +7453,22 @@
         <v>35</v>
       </c>
       <c r="C37" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="D37" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E37" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>0</v>
       </c>
       <c r="G37" t="s">
         <v>124</v>
       </c>
       <c r="H37" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PASTA P/DETECTAR GASOLINA</v>
       </c>
       <c r="I37" s="2">
@@ -6365,7 +7481,7 @@
         <v>96</v>
       </c>
       <c r="M37" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CALIBRADORES GRIPPER A/A</v>
       </c>
       <c r="N37" s="2">
@@ -6395,22 +7511,22 @@
         <v>36</v>
       </c>
       <c r="C38" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D38" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E38" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>1</v>
       </c>
       <c r="G38" t="s">
         <v>125</v>
       </c>
       <c r="H38" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PASTA P/DETECTAR AGUA</v>
       </c>
       <c r="I38" s="2">
@@ -6423,7 +7539,7 @@
         <v>96</v>
       </c>
       <c r="M38" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CALIBRADORES GRIPPER A/A</v>
       </c>
       <c r="N38" s="2">
@@ -6453,22 +7569,22 @@
         <v>37</v>
       </c>
       <c r="C39" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D39" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E39" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>1</v>
       </c>
       <c r="G39" t="s">
         <v>126</v>
       </c>
       <c r="H39" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">EPOXICO </v>
       </c>
       <c r="I39" s="2">
@@ -6481,7 +7597,7 @@
         <v>185</v>
       </c>
       <c r="M39" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">SHUT P/ AIRE </v>
       </c>
       <c r="N39" s="2">
@@ -6511,22 +7627,22 @@
         <v>38</v>
       </c>
       <c r="C40" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>13</v>
       </c>
       <c r="D40" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E40" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>13</v>
       </c>
       <c r="G40" t="s">
         <v>127</v>
       </c>
       <c r="H40" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>KIT DE EMPAQUE PARA MEDIDOR HELIX 4 PULGADAS</v>
       </c>
       <c r="I40" s="2">
@@ -6539,7 +7655,7 @@
         <v>185</v>
       </c>
       <c r="M40" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">SHUT P/ AIRE </v>
       </c>
       <c r="N40" s="2">
@@ -6569,22 +7685,22 @@
         <v>39</v>
       </c>
       <c r="C41" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>50</v>
       </c>
       <c r="D41" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E41" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>50</v>
       </c>
       <c r="G41" t="s">
         <v>128</v>
       </c>
       <c r="H41" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>EMPAQUES P/ DIISPENSAROI HELIX 1 PULGADA 22 MM</v>
       </c>
       <c r="I41" s="2">
@@ -6597,7 +7713,7 @@
         <v>98</v>
       </c>
       <c r="M41" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERAS AZULES A/A</v>
       </c>
       <c r="N41" s="2">
@@ -6627,22 +7743,22 @@
         <v>40</v>
       </c>
       <c r="C42" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>60</v>
       </c>
       <c r="D42" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E42" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>60</v>
       </c>
       <c r="G42" t="s">
         <v>129</v>
       </c>
       <c r="H42" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">EMPAQUES ORING DE MEDIDOR </v>
       </c>
       <c r="I42" s="2">
@@ -6655,7 +7771,7 @@
         <v>170</v>
       </c>
       <c r="M42" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">MANGUERAS DE DESCARGA </v>
       </c>
       <c r="N42" s="2">
@@ -6685,22 +7801,22 @@
         <v>41</v>
       </c>
       <c r="C43" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>26</v>
       </c>
       <c r="D43" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E43" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>26</v>
       </c>
       <c r="G43" t="s">
         <v>130</v>
       </c>
       <c r="H43" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">EMPAQUES ORING DE 1 PULGADA </v>
       </c>
       <c r="I43" s="2">
@@ -6713,7 +7829,7 @@
         <v>113</v>
       </c>
       <c r="M43" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>RADIOS MAG ONE</v>
       </c>
       <c r="N43" s="2">
@@ -6743,22 +7859,22 @@
         <v>42</v>
       </c>
       <c r="C44" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>10</v>
       </c>
       <c r="D44" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E44" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>10</v>
       </c>
       <c r="G44" t="s">
         <v>131</v>
       </c>
       <c r="H44" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">EMPAQUES P/MEDIDOR </v>
       </c>
       <c r="I44" s="2">
@@ -6771,7 +7887,7 @@
         <v>185</v>
       </c>
       <c r="M44" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">SHUT P/ AIRE </v>
       </c>
       <c r="N44" s="2">
@@ -6801,22 +7917,22 @@
         <v>43</v>
       </c>
       <c r="C45" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D45" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E45" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>1</v>
       </c>
       <c r="G45" t="s">
         <v>132</v>
       </c>
       <c r="H45" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MODULO RS232PARA VEEDER</v>
       </c>
       <c r="I45" s="2">
@@ -6829,7 +7945,7 @@
         <v>165</v>
       </c>
       <c r="M45" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>FILTRO GASOLINA BENNET 10 MICRAS</v>
       </c>
       <c r="N45" s="2">
@@ -6859,22 +7975,22 @@
         <v>44</v>
       </c>
       <c r="C46" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>5</v>
       </c>
       <c r="D46" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E46" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>5</v>
       </c>
       <c r="G46" t="s">
         <v>133</v>
       </c>
       <c r="H46" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MICRO SWITCH</v>
       </c>
       <c r="I46" s="2">
@@ -6887,7 +8003,7 @@
         <v>138</v>
       </c>
       <c r="M46" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PISTOLAS P/AGUA NEGRA</v>
       </c>
       <c r="N46" s="2">
@@ -6917,22 +8033,22 @@
         <v>45</v>
       </c>
       <c r="C47" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>18</v>
       </c>
       <c r="D47" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E47" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>18</v>
       </c>
       <c r="G47" t="s">
         <v>134</v>
       </c>
       <c r="H47" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>GLANDULAS 1/4 P/TAPA DE SELLADO HERMETICO</v>
       </c>
       <c r="I47" s="2">
@@ -6945,7 +8061,7 @@
         <v>117</v>
       </c>
       <c r="M47" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PALANCAS DE ACTIVACION PARA DIESEL WAYNE</v>
       </c>
       <c r="N47" s="2">
@@ -6975,22 +8091,22 @@
         <v>46</v>
       </c>
       <c r="C48" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>67</v>
       </c>
       <c r="D48" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>2</v>
       </c>
       <c r="E48" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>65</v>
       </c>
       <c r="G48" t="s">
         <v>135</v>
       </c>
       <c r="H48" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>FUSIBLE O PATITA DE SHUT-OFF</v>
       </c>
       <c r="I48" s="2">
@@ -7003,7 +8119,7 @@
         <v>97</v>
       </c>
       <c r="M48" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERAS VERDES A/A</v>
       </c>
       <c r="N48" s="2">
@@ -7033,22 +8149,22 @@
         <v>47</v>
       </c>
       <c r="C49" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>8</v>
       </c>
       <c r="D49" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>6</v>
       </c>
       <c r="E49" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>2</v>
       </c>
       <c r="G49" t="s">
         <v>136</v>
       </c>
       <c r="H49" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>SHUT P/AIRE DE DIESEL</v>
       </c>
       <c r="I49" s="2">
@@ -7061,7 +8177,7 @@
         <v>185</v>
       </c>
       <c r="M49" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">SHUT P/ AIRE </v>
       </c>
       <c r="N49" s="2">
@@ -7091,22 +8207,22 @@
         <v>48</v>
       </c>
       <c r="C50" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>6</v>
       </c>
       <c r="D50" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E50" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>6</v>
       </c>
       <c r="G50" t="s">
         <v>137</v>
       </c>
       <c r="H50" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>VALVULAS P/AIRE MOD. ANTERIOR</v>
       </c>
       <c r="I50" s="2">
@@ -7119,7 +8235,7 @@
         <v>97</v>
       </c>
       <c r="M50" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERAS VERDES A/A</v>
       </c>
       <c r="N50" s="2">
@@ -7149,22 +8265,22 @@
         <v>49</v>
       </c>
       <c r="C51" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>50</v>
       </c>
       <c r="D51" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>17</v>
       </c>
       <c r="E51" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>33</v>
       </c>
       <c r="G51" t="s">
         <v>138</v>
       </c>
       <c r="H51" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PISTOLAS P/AGUA NEGRA</v>
       </c>
       <c r="I51" s="2">
@@ -7177,7 +8293,7 @@
         <v>185</v>
       </c>
       <c r="M51" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">SHUT P/ AIRE </v>
       </c>
       <c r="N51" s="2">
@@ -7207,22 +8323,22 @@
         <v>50</v>
       </c>
       <c r="C52" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="D52" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E52" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>0</v>
       </c>
       <c r="G52" t="s">
         <v>139</v>
       </c>
       <c r="H52" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PISTOLA P/AGUA AZUL</v>
       </c>
       <c r="I52" s="2">
@@ -7235,7 +8351,7 @@
         <v>138</v>
       </c>
       <c r="M52" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PISTOLAS P/AGUA NEGRA</v>
       </c>
       <c r="N52" s="2">
@@ -7265,22 +8381,22 @@
         <v>51</v>
       </c>
       <c r="C53" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>22</v>
       </c>
       <c r="D53" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
-        <v>0</v>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
+        <v>4</v>
       </c>
       <c r="E53" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
-        <v>22</v>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
+        <v>18</v>
       </c>
       <c r="G53" t="s">
         <v>140</v>
       </c>
       <c r="H53" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>EMPAQUES P/ CAMPANAS DE DESCARGA</v>
       </c>
       <c r="I53" s="2">
@@ -7293,7 +8409,7 @@
         <v>159</v>
       </c>
       <c r="M53" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERAS DE GASOLINA</v>
       </c>
       <c r="N53" s="2">
@@ -7323,22 +8439,22 @@
         <v>52</v>
       </c>
       <c r="C54" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="D54" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E54" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>0</v>
       </c>
       <c r="G54" t="s">
         <v>141</v>
       </c>
       <c r="H54" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>BATERIAS P/VEEDER-ROOT</v>
       </c>
       <c r="I54" s="2">
@@ -7351,7 +8467,7 @@
         <v>169</v>
       </c>
       <c r="M54" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>DESTORCEDORES 3/4 GASOLINA OPW</v>
       </c>
       <c r="N54" s="2">
@@ -7381,22 +8497,22 @@
         <v>387</v>
       </c>
       <c r="C55" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D55" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E55" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>1</v>
       </c>
       <c r="G55" t="s">
         <v>142</v>
       </c>
       <c r="H55" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>RESORTE P/PALANCA HORIZON BENNET</v>
       </c>
       <c r="I55" s="2">
@@ -7409,7 +8525,7 @@
         <v>113</v>
       </c>
       <c r="M55" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>RADIOS MAG ONE</v>
       </c>
       <c r="N55" s="2">
@@ -7439,22 +8555,22 @@
         <v>53</v>
       </c>
       <c r="C56" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>3</v>
       </c>
       <c r="D56" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="E56" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>2</v>
       </c>
       <c r="G56" t="s">
         <v>143</v>
       </c>
       <c r="H56" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CABLES DE COMUNICACIÓN P/PROVETA VEEDER ROOT</v>
       </c>
       <c r="I56" s="2">
@@ -7467,7 +8583,7 @@
         <v>147</v>
       </c>
       <c r="M56" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>VALVULAS WAYNE SKINER HELIX W2893703-001</v>
       </c>
       <c r="N56" s="2">
@@ -7497,22 +8613,22 @@
         <v>54</v>
       </c>
       <c r="C57" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>3</v>
       </c>
       <c r="D57" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E57" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>3</v>
       </c>
       <c r="G57" t="s">
         <v>144</v>
       </c>
       <c r="H57" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CARTUCHO DE 1.5 HP</v>
       </c>
       <c r="I57" s="2">
@@ -7525,7 +8641,7 @@
         <v>316</v>
       </c>
       <c r="M57" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>BATERIA PARA RADIOS MAG ONE</v>
       </c>
       <c r="N57" s="2">
@@ -7555,22 +8671,22 @@
         <v>388</v>
       </c>
       <c r="C58" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>5</v>
       </c>
       <c r="D58" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>3</v>
       </c>
       <c r="E58" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>2</v>
       </c>
       <c r="G58" t="s">
         <v>145</v>
       </c>
       <c r="H58" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>VALVULAS SKINER DE DIESEL DE 2 HILOS CURVA ATLANTIC</v>
       </c>
       <c r="I58" s="2">
@@ -7583,7 +8699,7 @@
         <v>113</v>
       </c>
       <c r="M58" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>RADIOS MAG ONE</v>
       </c>
       <c r="N58" s="2">
@@ -7613,22 +8729,22 @@
         <v>55</v>
       </c>
       <c r="C59" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>10</v>
       </c>
       <c r="D59" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="E59" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>9</v>
       </c>
       <c r="G59" t="s">
         <v>146</v>
       </c>
       <c r="H59" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>SENSORES UNIVERSALES GRIS</v>
       </c>
       <c r="I59" s="2">
@@ -7641,7 +8757,7 @@
         <v>97</v>
       </c>
       <c r="M59" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERAS VERDES A/A</v>
       </c>
       <c r="N59" s="2">
@@ -7671,22 +8787,22 @@
         <v>871</v>
       </c>
       <c r="C60" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>22</v>
       </c>
       <c r="D60" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>4</v>
       </c>
       <c r="E60" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>18</v>
       </c>
       <c r="G60" t="s">
         <v>147</v>
       </c>
       <c r="H60" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>VALVULAS WAYNE SKINER HELIX W2893703-001</v>
       </c>
       <c r="I60" s="2">
@@ -7699,7 +8815,7 @@
         <v>185</v>
       </c>
       <c r="M60" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">SHUT P/ AIRE </v>
       </c>
       <c r="N60" s="2">
@@ -7729,22 +8845,22 @@
         <v>56</v>
       </c>
       <c r="C61" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>19</v>
       </c>
       <c r="D61" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="E61" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>18</v>
       </c>
       <c r="G61" t="s">
         <v>148</v>
       </c>
       <c r="H61" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>TAPAS GRISES CON CONEXIÓN GLANDULAR</v>
       </c>
       <c r="I61" s="2">
@@ -7757,7 +8873,7 @@
         <v>138</v>
       </c>
       <c r="M61" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PISTOLAS P/AGUA NEGRA</v>
       </c>
       <c r="N61" s="2">
@@ -7787,22 +8903,22 @@
         <v>57</v>
       </c>
       <c r="C62" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="D62" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E62" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>0</v>
       </c>
       <c r="G62" t="s">
         <v>149</v>
       </c>
       <c r="H62" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CONTENEDOR DE DERRAMES DE 5 GALONES OPW</v>
       </c>
       <c r="I62" s="2">
@@ -7815,7 +8931,7 @@
         <v>96</v>
       </c>
       <c r="M62" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CALIBRADORES GRIPPER A/A</v>
       </c>
       <c r="N62" s="2">
@@ -7845,22 +8961,22 @@
         <v>58</v>
       </c>
       <c r="C63" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>2</v>
       </c>
       <c r="D63" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E63" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>2</v>
       </c>
       <c r="G63" t="s">
         <v>150</v>
       </c>
       <c r="H63" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CONTENEDOR DE DERRAMES DE 5 GALONES UNIVERSAL</v>
       </c>
       <c r="I63" s="2">
@@ -7873,7 +8989,7 @@
         <v>287</v>
       </c>
       <c r="M63" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>VALVULA SKINNER RECTA DE 2 HILOS 24V #135461 PACIFIC</v>
       </c>
       <c r="N63" s="2">
@@ -7903,22 +9019,22 @@
         <v>59</v>
       </c>
       <c r="C64" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D64" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E64" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>1</v>
       </c>
       <c r="G64" t="s">
         <v>151</v>
       </c>
       <c r="H64" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CONTENEDOR DE DERRAMES DE 10 GALONES OPW</v>
       </c>
       <c r="I64" s="2">
@@ -7931,7 +9047,7 @@
         <v>288</v>
       </c>
       <c r="M64" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>TROMPA DE COCHINO CODO DE DESCARGA</v>
       </c>
       <c r="N64" s="2">
@@ -7961,22 +9077,22 @@
         <v>60</v>
       </c>
       <c r="C65" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>2</v>
       </c>
       <c r="D65" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E65" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>2</v>
       </c>
       <c r="G65" t="s">
         <v>152</v>
       </c>
       <c r="H65" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CODO DE DESCARGA</v>
       </c>
       <c r="I65" s="2">
@@ -7989,7 +9105,7 @@
         <v>318</v>
       </c>
       <c r="M65" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CHAPA PARA DISPENSARIO WAYNE</v>
       </c>
       <c r="N65" s="2">
@@ -8019,22 +9135,22 @@
         <v>61</v>
       </c>
       <c r="C66" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>44</v>
       </c>
       <c r="D66" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="E66" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>43</v>
       </c>
       <c r="G66" t="s">
         <v>153</v>
       </c>
       <c r="H66" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>TITIFLEX 1 1/2 X 24 PULGADAS</v>
       </c>
       <c r="I66" s="2">
@@ -8047,7 +9163,7 @@
         <v>317</v>
       </c>
       <c r="M66" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CONTROL PARA DISPENSARIO WAYNE</v>
       </c>
       <c r="N66" s="2">
@@ -8077,22 +9193,22 @@
         <v>62</v>
       </c>
       <c r="C67" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>14</v>
       </c>
       <c r="D67" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E67" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>14</v>
       </c>
       <c r="G67" t="s">
         <v>154</v>
       </c>
       <c r="H67" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>VALVULAS SKINER P/BENNET 3 HILOS</v>
       </c>
       <c r="I67" s="2">
@@ -8105,7 +9221,7 @@
         <v>293</v>
       </c>
       <c r="M67" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>DISPLAY DE VENTAS PACIFIC (REUSABLES)</v>
       </c>
       <c r="N67" s="2">
@@ -8135,22 +9251,22 @@
         <v>63</v>
       </c>
       <c r="C68" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>74</v>
       </c>
       <c r="D68" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E68" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>74</v>
       </c>
       <c r="G68" t="s">
         <v>155</v>
       </c>
       <c r="H68" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>FUNDAS PISTOLA VERDE</v>
       </c>
       <c r="I68" s="2">
@@ -8163,7 +9279,7 @@
         <v>185</v>
       </c>
       <c r="M68" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">SHUT P/ AIRE </v>
       </c>
       <c r="N68" s="2">
@@ -8193,22 +9309,22 @@
         <v>64</v>
       </c>
       <c r="C69" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>76</v>
       </c>
       <c r="D69" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E69" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>76</v>
       </c>
       <c r="G69" t="s">
         <v>156</v>
       </c>
       <c r="H69" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>FUNDAS PISTOLA ROJA</v>
       </c>
       <c r="I69" s="2">
@@ -8221,7 +9337,7 @@
         <v>97</v>
       </c>
       <c r="M69" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERAS VERDES A/A</v>
       </c>
       <c r="N69" s="2">
@@ -8251,22 +9367,22 @@
         <v>65</v>
       </c>
       <c r="C70" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>36</v>
       </c>
       <c r="D70" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E70" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>36</v>
       </c>
       <c r="G70" t="s">
         <v>157</v>
       </c>
       <c r="H70" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>FUNDAS NEGRAS 1"</v>
       </c>
       <c r="I70" s="2">
@@ -8279,7 +9395,7 @@
         <v>185</v>
       </c>
       <c r="M70" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">SHUT P/ AIRE </v>
       </c>
       <c r="N70" s="2">
@@ -8309,22 +9425,22 @@
         <v>66</v>
       </c>
       <c r="C71" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>30</v>
       </c>
       <c r="D71" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>2</v>
       </c>
       <c r="E71" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>28</v>
       </c>
       <c r="G71" t="s">
         <v>158</v>
       </c>
       <c r="H71" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERAS DE DIESEL</v>
       </c>
       <c r="I71" s="2">
@@ -8337,7 +9453,7 @@
         <v>97</v>
       </c>
       <c r="M71" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERAS VERDES A/A</v>
       </c>
       <c r="N71" s="2">
@@ -8367,22 +9483,22 @@
         <v>67</v>
       </c>
       <c r="C72" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
-        <v>10</v>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
+        <v>30</v>
       </c>
       <c r="D72" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
-        <v>11</v>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
+        <v>12</v>
       </c>
       <c r="E72" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
-        <v>-1</v>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
+        <v>18</v>
       </c>
       <c r="G72" t="s">
         <v>159</v>
       </c>
       <c r="H72" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERAS DE GASOLINA</v>
       </c>
       <c r="I72" s="2">
@@ -8395,7 +9511,7 @@
         <v>307</v>
       </c>
       <c r="M72" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>TARJETA DE RELEVADORES WAYNE (REUSABLES-USADAS)</v>
       </c>
       <c r="N72" s="2">
@@ -8425,22 +9541,22 @@
         <v>68</v>
       </c>
       <c r="C73" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>21</v>
       </c>
       <c r="D73" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E73" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>21</v>
       </c>
       <c r="G73" t="s">
         <v>160</v>
       </c>
       <c r="H73" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>BOTA FLEXBLE 1 PULGADA A 3/4</v>
       </c>
       <c r="I73" s="2">
@@ -8453,7 +9569,7 @@
         <v>105</v>
       </c>
       <c r="M73" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PULSADORES P/ DISPENSARIO BENNET</v>
       </c>
       <c r="N73" s="2">
@@ -8483,22 +9599,22 @@
         <v>69</v>
       </c>
       <c r="C74" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>14</v>
       </c>
       <c r="D74" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E74" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>14</v>
       </c>
       <c r="G74" t="s">
         <v>161</v>
       </c>
       <c r="H74" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>BOTA FLEXBLE 2 PULGADA</v>
       </c>
       <c r="I74" s="2">
@@ -8511,7 +9627,7 @@
         <v>100</v>
       </c>
       <c r="M74" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PISTOLA DE 3/4 P/GASOLINA</v>
       </c>
       <c r="N74" s="2">
@@ -8541,22 +9657,22 @@
         <v>70</v>
       </c>
       <c r="C75" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>30</v>
       </c>
       <c r="D75" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E75" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>30</v>
       </c>
       <c r="G75" t="s">
         <v>162</v>
       </c>
       <c r="H75" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>BOTA FLEXBLE 4 PULGADA 1 1/2</v>
       </c>
       <c r="I75" s="2">
@@ -8569,7 +9685,7 @@
         <v>158</v>
       </c>
       <c r="M75" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERAS DE DIESEL</v>
       </c>
       <c r="N75" s="2">
@@ -8599,22 +9715,22 @@
         <v>71</v>
       </c>
       <c r="C76" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D76" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E76" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>1</v>
       </c>
       <c r="G76" t="s">
         <v>163</v>
       </c>
       <c r="H76" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>BOTA DE PRUEBA DE 1 1/2 PULGADA</v>
       </c>
       <c r="I76" s="2">
@@ -8627,7 +9743,7 @@
         <v>159</v>
       </c>
       <c r="M76" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERAS DE GASOLINA</v>
       </c>
       <c r="N76" s="2">
@@ -8657,22 +9773,22 @@
         <v>72</v>
       </c>
       <c r="C77" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>24</v>
       </c>
       <c r="D77" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E77" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>24</v>
       </c>
       <c r="G77" t="s">
         <v>164</v>
       </c>
       <c r="H77" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>FILTRO DE ALTO FLUJO DIESEL WAYNE</v>
       </c>
       <c r="I77" s="2">
@@ -8685,7 +9801,7 @@
         <v>100</v>
       </c>
       <c r="M77" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PISTOLA DE 3/4 P/GASOLINA</v>
       </c>
       <c r="N77" s="2">
@@ -8715,22 +9831,22 @@
         <v>73</v>
       </c>
       <c r="C78" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>24</v>
       </c>
       <c r="D78" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>16</v>
       </c>
       <c r="E78" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>8</v>
       </c>
       <c r="G78" t="s">
         <v>165</v>
       </c>
       <c r="H78" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>FILTRO GASOLINA BENNET 10 MICRAS</v>
       </c>
       <c r="I78" s="2">
@@ -8743,7 +9859,7 @@
         <v>101</v>
       </c>
       <c r="M78" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PISTOLA DE 1 PULGADA P/DIESEL</v>
       </c>
       <c r="N78" s="2">
@@ -8773,22 +9889,22 @@
         <v>74</v>
       </c>
       <c r="C79" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>24</v>
       </c>
       <c r="D79" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E79" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>24</v>
       </c>
       <c r="G79" t="s">
         <v>166</v>
       </c>
       <c r="H79" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>FILTRO GASOLINA BENNET 30 MICRAS</v>
       </c>
       <c r="I79" s="2">
@@ -8801,7 +9917,7 @@
         <v>118</v>
       </c>
       <c r="M79" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>DESTORCEDOR DE DIESEL 1 PULGADA OPW CODO</v>
       </c>
       <c r="N79" s="2">
@@ -8831,22 +9947,22 @@
         <v>75</v>
       </c>
       <c r="C80" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>120</v>
       </c>
       <c r="D80" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
-        <v>0</v>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
+        <v>3</v>
       </c>
       <c r="E80" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
-        <v>120</v>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
+        <v>117</v>
       </c>
       <c r="G80" t="s">
         <v>167</v>
       </c>
       <c r="H80" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>FILTRO GASOLINA WAYNE 10 MICRAS</v>
       </c>
       <c r="I80" s="2">
@@ -8859,7 +9975,7 @@
         <v>169</v>
       </c>
       <c r="M80" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>DESTORCEDORES 3/4 GASOLINA OPW</v>
       </c>
       <c r="N80" s="2">
@@ -8889,22 +10005,22 @@
         <v>76</v>
       </c>
       <c r="C81" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>84</v>
       </c>
       <c r="D81" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
-        <v>0</v>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
+        <v>2</v>
       </c>
       <c r="E81" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
-        <v>84</v>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
+        <v>82</v>
       </c>
       <c r="G81" t="s">
         <v>168</v>
       </c>
       <c r="H81" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>FILTRO DIESEL WAYNE 30 MICRAS CIMTEK</v>
       </c>
       <c r="I81" s="2">
@@ -8917,7 +10033,7 @@
         <v>147</v>
       </c>
       <c r="M81" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>VALVULAS WAYNE SKINER HELIX W2893703-001</v>
       </c>
       <c r="N81" s="2">
@@ -8947,22 +10063,22 @@
         <v>77</v>
       </c>
       <c r="C82" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>23</v>
       </c>
       <c r="D82" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
-        <v>15</v>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
+        <v>17</v>
       </c>
       <c r="E82" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
-        <v>8</v>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
+        <v>6</v>
       </c>
       <c r="G82" t="s">
         <v>169</v>
       </c>
       <c r="H82" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>DESTORCEDORES 3/4 GASOLINA OPW</v>
       </c>
       <c r="I82" s="2">
@@ -8975,7 +10091,7 @@
         <v>145</v>
       </c>
       <c r="M82" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>VALVULAS SKINER DE DIESEL DE 2 HILOS CURVA ATLANTIC</v>
       </c>
       <c r="N82" s="2">
@@ -9005,22 +10121,22 @@
         <v>78</v>
       </c>
       <c r="C83" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>4</v>
       </c>
       <c r="D83" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="E83" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>3</v>
       </c>
       <c r="G83" t="s">
         <v>170</v>
       </c>
       <c r="H83" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">MANGUERAS DE DESCARGA </v>
       </c>
       <c r="I83" s="2">
@@ -9033,7 +10149,7 @@
         <v>118</v>
       </c>
       <c r="M83" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>DESTORCEDOR DE DIESEL 1 PULGADA OPW CODO</v>
       </c>
       <c r="N83" s="2">
@@ -9063,22 +10179,22 @@
         <v>79</v>
       </c>
       <c r="C84" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>4</v>
       </c>
       <c r="D84" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="E84" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>3</v>
       </c>
       <c r="G84" t="s">
         <v>171</v>
       </c>
       <c r="H84" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CONTADORAS DE MONEDAS</v>
       </c>
       <c r="I84" s="2">
@@ -9091,7 +10207,7 @@
         <v>100</v>
       </c>
       <c r="M84" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PISTOLA DE 3/4 P/GASOLINA</v>
       </c>
       <c r="N84" s="2">
@@ -9121,22 +10237,22 @@
         <v>80</v>
       </c>
       <c r="C85" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D85" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="E85" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>0</v>
       </c>
       <c r="G85" t="s">
         <v>172</v>
       </c>
       <c r="H85" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>COMPRESOR HORIZONTAL (PRUEBAS)</v>
       </c>
       <c r="I85" s="2">
@@ -9149,7 +10265,7 @@
         <v>159</v>
       </c>
       <c r="M85" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERAS DE GASOLINA</v>
       </c>
       <c r="N85" s="2">
@@ -9179,22 +10295,22 @@
         <v>81</v>
       </c>
       <c r="C86" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>11</v>
       </c>
       <c r="D86" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E86" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>11</v>
       </c>
       <c r="G86" t="s">
         <v>173</v>
       </c>
       <c r="H86" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">COPLE ELECTRICO DE 3/4 X 18 </v>
       </c>
       <c r="I86" s="2">
@@ -9207,7 +10323,7 @@
         <v>159</v>
       </c>
       <c r="M86" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERAS DE GASOLINA</v>
       </c>
       <c r="N86" s="2">
@@ -9237,22 +10353,22 @@
         <v>82</v>
       </c>
       <c r="C87" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D87" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E87" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>1</v>
       </c>
       <c r="G87" t="s">
         <v>174</v>
       </c>
       <c r="H87" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>COPLE ELECTRICO DE 3/4 X 21</v>
       </c>
       <c r="I87" s="2">
@@ -9265,7 +10381,7 @@
         <v>319</v>
       </c>
       <c r="M87" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>REDUCCION DE CAMPANA 3/4"</v>
       </c>
       <c r="N87" s="2">
@@ -9295,22 +10411,22 @@
         <v>83</v>
       </c>
       <c r="C88" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D88" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E88" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>1</v>
       </c>
       <c r="G88" t="s">
         <v>175</v>
       </c>
       <c r="H88" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>COPLE ELECTRICO DE 3/4 X 30</v>
       </c>
       <c r="I88" s="2">
@@ -9323,7 +10439,7 @@
         <v>320</v>
       </c>
       <c r="M88" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>NIPLE ROSCA CORRIDA 3/4"</v>
       </c>
       <c r="N88" s="2">
@@ -9353,22 +10469,22 @@
         <v>84</v>
       </c>
       <c r="C89" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D89" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E89" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>1</v>
       </c>
       <c r="G89" t="s">
         <v>176</v>
       </c>
       <c r="H89" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>TITIFLEX DE 1 1/2 X 20</v>
       </c>
       <c r="I89" s="2">
@@ -9381,7 +10497,7 @@
         <v>321</v>
       </c>
       <c r="M89" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>FUNDA NEGRA DE 3/4"</v>
       </c>
       <c r="N89" s="2">
@@ -9411,22 +10527,22 @@
         <v>85</v>
       </c>
       <c r="C90" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>4</v>
       </c>
       <c r="D90" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E90" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>4</v>
       </c>
       <c r="G90" t="s">
         <v>177</v>
       </c>
       <c r="H90" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>TITIFLEX DE 1 1/2 X 18</v>
       </c>
       <c r="I90" s="2">
@@ -9439,7 +10555,7 @@
         <v>100</v>
       </c>
       <c r="M90" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PISTOLA DE 3/4 P/GASOLINA</v>
       </c>
       <c r="N90" s="2">
@@ -9469,22 +10585,22 @@
         <v>86</v>
       </c>
       <c r="C91" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>12</v>
       </c>
       <c r="D91" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E91" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>12</v>
       </c>
       <c r="G91" t="s">
         <v>178</v>
       </c>
       <c r="H91" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>TAPAS DE DISPENSARIO BENNET</v>
       </c>
       <c r="I91" s="2">
@@ -9497,7 +10613,7 @@
         <v>322</v>
       </c>
       <c r="M91" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERA NEGRA AGUA Y AIRE</v>
       </c>
       <c r="N91" s="2">
@@ -9527,22 +10643,22 @@
         <v>87</v>
       </c>
       <c r="C92" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>3</v>
       </c>
       <c r="D92" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>3</v>
       </c>
       <c r="E92" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>0</v>
       </c>
       <c r="G92" t="s">
         <v>179</v>
       </c>
       <c r="H92" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>REGISTROS OPW 12 PULGADAS</v>
       </c>
       <c r="I92" s="2">
@@ -9555,7 +10671,7 @@
         <v>323</v>
       </c>
       <c r="M92" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>SHUT DE AIRE DISP. MECANICO</v>
       </c>
       <c r="N92" s="2">
@@ -9585,22 +10701,22 @@
         <v>88</v>
       </c>
       <c r="C93" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>2</v>
       </c>
       <c r="D93" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E93" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>2</v>
       </c>
       <c r="G93" t="s">
         <v>180</v>
       </c>
       <c r="H93" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CONSOLAS VEDEER ROOT</v>
       </c>
       <c r="I93" s="2">
@@ -9613,7 +10729,7 @@
         <v>138</v>
       </c>
       <c r="M93" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PISTOLAS P/AGUA NEGRA</v>
       </c>
       <c r="N93" s="2">
@@ -9643,22 +10759,22 @@
         <v>89</v>
       </c>
       <c r="C94" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>2</v>
       </c>
       <c r="D94" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="E94" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>1</v>
       </c>
       <c r="G94" t="s">
         <v>181</v>
       </c>
       <c r="H94" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">DISPENSARIOS DE AGUA Y AIRE </v>
       </c>
       <c r="I94" s="2">
@@ -9671,7 +10787,7 @@
         <v>324</v>
       </c>
       <c r="M94" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERA LARGA DE DIESEL 6M</v>
       </c>
       <c r="N94" s="2">
@@ -9701,22 +10817,22 @@
         <v>90</v>
       </c>
       <c r="C95" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D95" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E95" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>1</v>
       </c>
       <c r="G95" t="s">
         <v>182</v>
       </c>
       <c r="H95" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>VALVULA DE VENTEO OPW 3 A 2</v>
       </c>
       <c r="I95" s="2">
@@ -9729,7 +10845,7 @@
         <v>325</v>
       </c>
       <c r="M95" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERA DE DESCARGA 6M</v>
       </c>
       <c r="N95" s="2">
@@ -9759,22 +10875,22 @@
         <v>91</v>
       </c>
       <c r="C96" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>8</v>
       </c>
       <c r="D96" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E96" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>8</v>
       </c>
       <c r="G96" t="s">
         <v>183</v>
       </c>
       <c r="H96" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>VALVULA DE RECUPERACION DE VAPORES</v>
       </c>
       <c r="I96" s="2">
@@ -9787,7 +10903,7 @@
         <v>326</v>
       </c>
       <c r="M96" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">UNIVERSAL VALVULA FLOTADORA 2 X 6 </v>
       </c>
       <c r="N96" s="2">
@@ -9817,22 +10933,22 @@
         <v>92</v>
       </c>
       <c r="C97" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>4</v>
       </c>
       <c r="D97" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E97" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>4</v>
       </c>
       <c r="G97" t="s">
         <v>184</v>
       </c>
       <c r="H97" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PICOS DE DIESEL 1"</v>
       </c>
       <c r="I97" s="2">
@@ -9845,7 +10961,7 @@
         <v>185</v>
       </c>
       <c r="M97" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">SHUT P/ AIRE </v>
       </c>
       <c r="N97" s="2">
@@ -9875,22 +10991,22 @@
         <v>93</v>
       </c>
       <c r="C98" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>53</v>
       </c>
       <c r="D98" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>32</v>
       </c>
       <c r="E98" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>21</v>
       </c>
       <c r="G98" t="s">
         <v>185</v>
       </c>
       <c r="H98" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">SHUT P/ AIRE </v>
       </c>
       <c r="I98" s="2">
@@ -9903,7 +11019,7 @@
         <v>96</v>
       </c>
       <c r="M98" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CALIBRADORES GRIPPER A/A</v>
       </c>
       <c r="N98" s="2">
@@ -9933,22 +11049,22 @@
         <v>94</v>
       </c>
       <c r="C99" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="D99" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E99" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>0</v>
       </c>
       <c r="G99" t="s">
         <v>186</v>
       </c>
       <c r="H99" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>EMPAQUE DE GORRITO</v>
       </c>
       <c r="I99" s="2">
@@ -9961,7 +11077,7 @@
         <v>159</v>
       </c>
       <c r="M99" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERAS DE GASOLINA</v>
       </c>
       <c r="N99" s="2">
@@ -9991,22 +11107,22 @@
         <v>95</v>
       </c>
       <c r="C100" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>10</v>
       </c>
       <c r="D100" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>6</v>
       </c>
       <c r="E100" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>4</v>
       </c>
       <c r="G100" t="s">
         <v>187</v>
       </c>
       <c r="H100" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>SENSOR LIQUIDO DE BRONCE</v>
       </c>
       <c r="I100" s="2">
@@ -10019,7 +11135,7 @@
         <v>97</v>
       </c>
       <c r="M100" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERAS VERDES A/A</v>
       </c>
       <c r="N100" s="2">
@@ -10049,22 +11165,22 @@
         <v>870</v>
       </c>
       <c r="C101" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>5</v>
       </c>
       <c r="D101" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>2</v>
       </c>
       <c r="E101" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>3</v>
       </c>
       <c r="G101" t="s">
         <v>287</v>
       </c>
       <c r="H101" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>VALVULA SKINNER RECTA DE 2 HILOS 24V #135461 PACIFIC</v>
       </c>
       <c r="I101" s="2">
@@ -10077,7 +11193,7 @@
         <v>169</v>
       </c>
       <c r="M101" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>DESTORCEDORES 3/4 GASOLINA OPW</v>
       </c>
       <c r="N101" s="2">
@@ -10107,22 +11223,22 @@
         <v>835</v>
       </c>
       <c r="C102" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>6</v>
       </c>
       <c r="D102" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>3</v>
       </c>
       <c r="E102" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>3</v>
       </c>
       <c r="G102" t="s">
         <v>152</v>
       </c>
       <c r="H102" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CODO DE DESCARGA</v>
       </c>
       <c r="I102" s="2">
@@ -10135,7 +11251,7 @@
         <v>145</v>
       </c>
       <c r="M102" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>VALVULAS SKINER DE DIESEL DE 2 HILOS CURVA ATLANTIC</v>
       </c>
       <c r="N102" s="2">
@@ -10165,22 +11281,22 @@
         <v>843</v>
       </c>
       <c r="C103" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>21</v>
       </c>
       <c r="D103" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E103" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>21</v>
       </c>
       <c r="G103" t="s">
         <v>117</v>
       </c>
       <c r="H103" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PALANCAS DE ACTIVACION PARA DIESEL WAYNE</v>
       </c>
       <c r="I103" s="2">
@@ -10193,7 +11309,7 @@
         <v>288</v>
       </c>
       <c r="M103" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>TROMPA DE COCHINO CODO DE DESCARGA</v>
       </c>
       <c r="N103" s="2">
@@ -10223,22 +11339,22 @@
         <v>844</v>
       </c>
       <c r="C104" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>2</v>
       </c>
       <c r="D104" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E104" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>2</v>
       </c>
       <c r="G104" t="s">
         <v>288</v>
       </c>
       <c r="H104" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>TROMPA DE COCHINO CODO DE DESCARGA</v>
       </c>
       <c r="I104" s="2">
@@ -10251,7 +11367,7 @@
         <v>327</v>
       </c>
       <c r="M104" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>ORING PARA VALVULA DE CORTE RAPIDO</v>
       </c>
       <c r="N104" s="2">
@@ -10281,22 +11397,22 @@
         <v>845</v>
       </c>
       <c r="C105" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>12</v>
       </c>
       <c r="D105" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E105" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>12</v>
       </c>
       <c r="G105" t="s">
         <v>96</v>
       </c>
       <c r="H105" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CALIBRADORES GRIPPER A/A</v>
       </c>
       <c r="I105" s="2">
@@ -10309,7 +11425,7 @@
         <v>185</v>
       </c>
       <c r="M105" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">SHUT P/ AIRE </v>
       </c>
       <c r="N105" s="2">
@@ -10339,22 +11455,22 @@
         <v>849</v>
       </c>
       <c r="C106" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>6</v>
       </c>
       <c r="D106" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E106" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>6</v>
       </c>
       <c r="G106" t="s">
         <v>181</v>
       </c>
       <c r="H106" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">DISPENSARIOS DE AGUA Y AIRE </v>
       </c>
       <c r="I106" s="2">
@@ -10367,7 +11483,7 @@
         <v>96</v>
       </c>
       <c r="M106" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CALIBRADORES GRIPPER A/A</v>
       </c>
       <c r="N106" s="2">
@@ -10397,22 +11513,22 @@
         <v>850</v>
       </c>
       <c r="C107" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>6</v>
       </c>
       <c r="D107" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="E107" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>5</v>
       </c>
       <c r="G107" t="s">
         <v>138</v>
       </c>
       <c r="H107" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PISTOLAS P/AGUA NEGRA</v>
       </c>
       <c r="I107" s="2">
@@ -10425,7 +11541,7 @@
         <v>159</v>
       </c>
       <c r="M107" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERAS DE GASOLINA</v>
       </c>
       <c r="N107" s="2">
@@ -10455,22 +11571,22 @@
         <v>851</v>
       </c>
       <c r="C108" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>14</v>
       </c>
       <c r="D108" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E108" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>14</v>
       </c>
       <c r="G108" t="s">
         <v>185</v>
       </c>
       <c r="H108" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">SHUT P/ AIRE </v>
       </c>
       <c r="I108" s="2">
@@ -10483,7 +11599,7 @@
         <v>169</v>
       </c>
       <c r="M108" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>DESTORCEDORES 3/4 GASOLINA OPW</v>
       </c>
       <c r="N108" s="2">
@@ -10513,22 +11629,22 @@
         <v>852</v>
       </c>
       <c r="C109" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D109" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E109" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>1</v>
       </c>
       <c r="G109" t="s">
         <v>103</v>
       </c>
       <c r="H109" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>BATERIAS DE 12 V P/DISPENSARIO BENNET</v>
       </c>
       <c r="I109" s="2">
@@ -10541,7 +11657,7 @@
         <v>145</v>
       </c>
       <c r="M109" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>VALVULAS SKINER DE DIESEL DE 2 HILOS CURVA ATLANTIC</v>
       </c>
       <c r="N109" s="2">
@@ -10571,22 +11687,22 @@
         <v>853</v>
       </c>
       <c r="C110" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>20</v>
       </c>
       <c r="D110" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E110" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>20</v>
       </c>
       <c r="G110" t="s">
         <v>143</v>
       </c>
       <c r="H110" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CABLES DE COMUNICACIÓN P/PROVETA VEEDER ROOT</v>
       </c>
       <c r="I110" s="2">
@@ -10599,7 +11715,7 @@
         <v>117</v>
       </c>
       <c r="M110" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PALANCAS DE ACTIVACION PARA DIESEL WAYNE</v>
       </c>
       <c r="N110" s="2">
@@ -10629,22 +11745,22 @@
         <v>854</v>
       </c>
       <c r="C111" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>18</v>
       </c>
       <c r="D111" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E111" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>18</v>
       </c>
       <c r="G111" t="s">
         <v>289</v>
       </c>
       <c r="H111" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MEDIDORES DE BENNET RU GASOLINA/DIESEL</v>
       </c>
       <c r="I111" s="2">
@@ -10657,7 +11773,7 @@
         <v>136</v>
       </c>
       <c r="M111" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>SHUT P/AIRE DE DIESEL</v>
       </c>
       <c r="N111" s="2">
@@ -10687,22 +11803,22 @@
         <v>855</v>
       </c>
       <c r="C112" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D112" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E112" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>1</v>
       </c>
       <c r="G112" t="s">
         <v>290</v>
       </c>
       <c r="H112" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MEDIDORES DE ALTO FLUJO BENNET DIESEL</v>
       </c>
       <c r="I112" s="2">
@@ -10715,7 +11831,7 @@
         <v>299</v>
       </c>
       <c r="M112" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>SR-232 TARJETA DE COMUNICACIÓN BENNETT (REUSABLES)</v>
       </c>
       <c r="N112" s="2">
@@ -10745,22 +11861,22 @@
         <v>856</v>
       </c>
       <c r="C113" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>15</v>
       </c>
       <c r="D113" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="E113" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>14</v>
       </c>
       <c r="G113" t="s">
         <v>291</v>
       </c>
       <c r="H113" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MEDIDORES WAYNE GASOLINA/DIESEL</v>
       </c>
       <c r="I113" s="2">
@@ -10773,7 +11889,7 @@
         <v>109</v>
       </c>
       <c r="M113" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>ADAPTADORES DE BRONCE DE 4 PULGADAS</v>
       </c>
       <c r="N113" s="2">
@@ -10803,22 +11919,22 @@
         <v>857</v>
       </c>
       <c r="C114" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>23</v>
       </c>
       <c r="D114" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E114" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>23</v>
       </c>
       <c r="G114" t="s">
         <v>292</v>
       </c>
       <c r="H114" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>TARJETAS BENNETT PACIFIC P/UNITARIOS (REUSABLES)</v>
       </c>
       <c r="I114" s="2">
@@ -10831,7 +11947,7 @@
         <v>148</v>
       </c>
       <c r="M114" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>TAPAS GRISES CON CONEXIÓN GLANDULAR</v>
       </c>
       <c r="N114" s="2">
@@ -10861,22 +11977,22 @@
         <v>858</v>
       </c>
       <c r="C115" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>20</v>
       </c>
       <c r="D115" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E115" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>20</v>
       </c>
       <c r="G115" t="s">
         <v>293</v>
       </c>
       <c r="H115" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>DISPLAY DE VENTAS PACIFIC (REUSABLES)</v>
       </c>
       <c r="I115" s="2">
@@ -10889,7 +12005,7 @@
         <v>100</v>
       </c>
       <c r="M115" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PISTOLA DE 3/4 P/GASOLINA</v>
       </c>
       <c r="N115" s="2">
@@ -10919,22 +12035,22 @@
         <v>859</v>
       </c>
       <c r="C116" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>5</v>
       </c>
       <c r="D116" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E116" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>5</v>
       </c>
       <c r="G116" t="s">
         <v>294</v>
       </c>
       <c r="H116" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CPU PACIFIC Y ATLANTIC (POR REPARAR)</v>
       </c>
       <c r="I116" s="2">
@@ -10947,7 +12063,7 @@
         <v>169</v>
       </c>
       <c r="M116" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>DESTORCEDORES 3/4 GASOLINA OPW</v>
       </c>
       <c r="N116" s="2">
@@ -10977,22 +12093,22 @@
         <v>860</v>
       </c>
       <c r="C117" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D117" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E117" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>1</v>
       </c>
       <c r="G117" t="s">
         <v>295</v>
       </c>
       <c r="H117" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CARCASA CON CPU COMPLETA PARA DIESEL NUEVA</v>
       </c>
       <c r="I117" s="2">
@@ -11005,7 +12121,7 @@
         <v>169</v>
       </c>
       <c r="M117" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>DESTORCEDORES 3/4 GASOLINA OPW</v>
       </c>
       <c r="N117" s="2">
@@ -11035,22 +12151,22 @@
         <v>861</v>
       </c>
       <c r="C118" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>2</v>
       </c>
       <c r="D118" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E118" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>2</v>
       </c>
       <c r="G118" t="s">
         <v>296</v>
       </c>
       <c r="H118" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>IMAN PARA VALVULAS SKINNER (REUSABLES)</v>
       </c>
       <c r="I118" s="2">
@@ -11063,7 +12179,7 @@
         <v>159</v>
       </c>
       <c r="M118" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERAS DE GASOLINA</v>
       </c>
       <c r="N118" s="2">
@@ -11093,22 +12209,22 @@
         <v>862</v>
       </c>
       <c r="C119" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>2</v>
       </c>
       <c r="D119" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E119" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>2</v>
       </c>
       <c r="G119" t="s">
         <v>297</v>
       </c>
       <c r="H119" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>FUENTES DE PODER BENNET (USADO)</v>
       </c>
       <c r="I119" s="2">
@@ -11121,7 +12237,7 @@
         <v>185</v>
       </c>
       <c r="M119" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">SHUT P/ AIRE </v>
       </c>
       <c r="N119" s="2">
@@ -11151,22 +12267,22 @@
         <v>863</v>
       </c>
       <c r="C120" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>5</v>
       </c>
       <c r="D120" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E120" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>5</v>
       </c>
       <c r="G120" t="s">
         <v>298</v>
       </c>
       <c r="H120" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MEDIDOR WAYNE GASOLINA/DIESEL (USADO-POR REPARAR)</v>
       </c>
       <c r="I120" s="2">
@@ -11179,7 +12295,7 @@
         <v>97</v>
       </c>
       <c r="M120" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERAS VERDES A/A</v>
       </c>
       <c r="N120" s="2">
@@ -11209,22 +12325,22 @@
         <v>864</v>
       </c>
       <c r="C121" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>3</v>
       </c>
       <c r="D121" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="E121" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>2</v>
       </c>
       <c r="G121" t="s">
         <v>299</v>
       </c>
       <c r="H121" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>SR-232 TARJETA DE COMUNICACIÓN BENNETT (REUSABLES)</v>
       </c>
       <c r="I121" s="2">
@@ -11237,7 +12353,7 @@
         <v>185</v>
       </c>
       <c r="M121" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">SHUT P/ AIRE </v>
       </c>
       <c r="N121" s="2">
@@ -11267,22 +12383,22 @@
         <v>865</v>
       </c>
       <c r="C122" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>4</v>
       </c>
       <c r="D122" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E122" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>4</v>
       </c>
       <c r="G122" t="s">
         <v>300</v>
       </c>
       <c r="H122" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>TECLADO PARA PRESET BENNETT (REUSABLES)</v>
       </c>
       <c r="I122" s="2">
@@ -11295,7 +12411,7 @@
         <v>185</v>
       </c>
       <c r="M122" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">SHUT P/ AIRE </v>
       </c>
       <c r="N122" s="2">
@@ -11325,22 +12441,22 @@
         <v>866</v>
       </c>
       <c r="C123" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>10</v>
       </c>
       <c r="D123" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E123" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>10</v>
       </c>
       <c r="G123" t="s">
         <v>301</v>
       </c>
       <c r="H123" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CARRETES DE LECTURAS BENNETT (USADOS)</v>
       </c>
       <c r="I123" s="2">
@@ -11353,7 +12469,7 @@
         <v>97</v>
       </c>
       <c r="M123" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERAS VERDES A/A</v>
       </c>
       <c r="N123" s="2">
@@ -11383,22 +12499,22 @@
         <v>867</v>
       </c>
       <c r="C124" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>2</v>
       </c>
       <c r="D124" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E124" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>2</v>
       </c>
       <c r="G124" t="s">
         <v>302</v>
       </c>
       <c r="H124" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>TARJETA LOWER BENNETT (REUSABLES)</v>
       </c>
       <c r="I124" s="2">
@@ -11411,7 +12527,7 @@
         <v>185</v>
       </c>
       <c r="M124" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">SHUT P/ AIRE </v>
       </c>
       <c r="N124" s="2">
@@ -11441,22 +12557,22 @@
         <v>868</v>
       </c>
       <c r="C125" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>10</v>
       </c>
       <c r="D125" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E125" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>10</v>
       </c>
       <c r="G125" t="s">
         <v>303</v>
       </c>
       <c r="H125" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>DISPLAY PARA DISP. HORIZON (REUSABLES)</v>
       </c>
       <c r="I125" s="2">
@@ -11469,7 +12585,7 @@
         <v>97</v>
       </c>
       <c r="M125" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERAS VERDES A/A</v>
       </c>
       <c r="N125" s="2">
@@ -11499,22 +12615,22 @@
         <v>869</v>
       </c>
       <c r="C126" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D126" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E126" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>1</v>
       </c>
       <c r="G126" t="s">
         <v>304</v>
       </c>
       <c r="H126" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>BARRERA INTRINSICA WAYNE HELIX 2 (REUSABLES-USADAS)</v>
       </c>
       <c r="I126" s="2">
@@ -11527,7 +12643,7 @@
         <v>100</v>
       </c>
       <c r="M126" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PISTOLA DE 3/4 P/GASOLINA</v>
       </c>
       <c r="N126" s="2">
@@ -11557,22 +12673,22 @@
         <v>846</v>
       </c>
       <c r="C127" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>2</v>
       </c>
       <c r="D127" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E127" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>2</v>
       </c>
       <c r="G127" t="s">
         <v>305</v>
       </c>
       <c r="H127" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>BARRERA INTRINSICA WAYNE OVATION (REUSABLES-USADAS)</v>
       </c>
       <c r="I127" s="2">
@@ -11585,7 +12701,7 @@
         <v>135</v>
       </c>
       <c r="M127" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>FUSIBLE O PATITA DE SHUT-OFF</v>
       </c>
       <c r="N127" s="2">
@@ -11615,22 +12731,22 @@
         <v>847</v>
       </c>
       <c r="C128" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>2</v>
       </c>
       <c r="D128" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E128" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>2</v>
       </c>
       <c r="G128" t="s">
         <v>306</v>
       </c>
       <c r="H128" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>FUENTE DE PODER PARA WAYNE HELIX (REUSABLES-USADAS)</v>
       </c>
       <c r="I128" s="2">
@@ -11643,7 +12759,7 @@
         <v>108</v>
       </c>
       <c r="M128" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>VALVULA DE CORTE DE 3/4 GASOLINA</v>
       </c>
       <c r="N128" s="2">
@@ -11673,22 +12789,22 @@
         <v>848</v>
       </c>
       <c r="C129" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>4</v>
       </c>
       <c r="D129" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E129" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>4</v>
       </c>
       <c r="G129" t="s">
         <v>307</v>
       </c>
       <c r="H129" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>TARJETA DE RELEVADORES WAYNE (REUSABLES-USADAS)</v>
       </c>
       <c r="I129" s="2">
@@ -11701,7 +12817,7 @@
         <v>135</v>
       </c>
       <c r="M129" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>FUSIBLE O PATITA DE SHUT-OFF</v>
       </c>
       <c r="N129" s="2">
@@ -11731,22 +12847,22 @@
         <v>878</v>
       </c>
       <c r="C130" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D130" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="E130" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>0</v>
       </c>
       <c r="G130" t="s">
         <v>308</v>
       </c>
       <c r="H130" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>TARJETAS DE CORRIENTE DIRECTA (REUSABLES-USADAS)</v>
       </c>
       <c r="I130" s="2">
@@ -11759,7 +12875,7 @@
         <v>117</v>
       </c>
       <c r="M130" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PALANCAS DE ACTIVACION PARA DIESEL WAYNE</v>
       </c>
       <c r="N130" s="2">
@@ -11789,22 +12905,22 @@
         <v>883</v>
       </c>
       <c r="C131" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D131" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="E131" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>0</v>
       </c>
       <c r="G131" t="s">
         <v>309</v>
       </c>
       <c r="H131" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>TARJETA DE PRECIOS UNITARIOS (REUSABLES-USADAS)</v>
       </c>
       <c r="I131" s="2">
@@ -11817,7 +12933,7 @@
         <v>165</v>
       </c>
       <c r="M131" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>FILTRO GASOLINA BENNET 10 MICRAS</v>
       </c>
       <c r="N131" s="2">
@@ -11847,22 +12963,22 @@
         <v>884</v>
       </c>
       <c r="C132" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>4</v>
       </c>
       <c r="D132" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>2</v>
       </c>
       <c r="E132" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>2</v>
       </c>
       <c r="G132" t="s">
         <v>310</v>
       </c>
       <c r="H132" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CPU WAYNE (REUSABLES-USADAS)</v>
       </c>
       <c r="I132" s="2">
@@ -11875,7 +12991,7 @@
         <v>113</v>
       </c>
       <c r="M132" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>RADIOS MAG ONE</v>
       </c>
       <c r="N132" s="2">
@@ -11905,22 +13021,22 @@
         <v>890</v>
       </c>
       <c r="C133" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D133" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="E133" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>0</v>
       </c>
       <c r="G133" t="s">
         <v>311</v>
       </c>
       <c r="H133" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>TARJETAS PARA PROGRAMAR TOTALES (REUSABLES-USADAS)</v>
       </c>
       <c r="I133" s="2">
@@ -11933,7 +13049,7 @@
         <v>97</v>
       </c>
       <c r="M133" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERAS VERDES A/A</v>
       </c>
       <c r="N133" s="2">
@@ -11963,22 +13079,22 @@
         <v>891</v>
       </c>
       <c r="C134" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D134" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="E134" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>0</v>
       </c>
       <c r="G134" t="s">
         <v>312</v>
       </c>
       <c r="H134" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CARRETE PARA DISP. WAYNE (REUSABLES-USADAS)</v>
       </c>
       <c r="I134" s="2">
@@ -11991,7 +13107,7 @@
         <v>138</v>
       </c>
       <c r="M134" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>PISTOLAS P/AGUA NEGRA</v>
       </c>
       <c r="N134" s="2">
@@ -12021,22 +13137,22 @@
         <v>892</v>
       </c>
       <c r="C135" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D135" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="E135" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>0</v>
       </c>
       <c r="G135" t="s">
         <v>313</v>
       </c>
       <c r="H135" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CPU OVATION WAYNE NUEVAS</v>
       </c>
       <c r="I135" s="2">
@@ -12045,9 +13161,30 @@
       <c r="J135" s="8">
         <v>2</v>
       </c>
+      <c r="L135" t="s">
+        <v>97</v>
+      </c>
       <c r="M135" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
-        <v>NO EXISTE</v>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
+        <v>MANGUERAS VERDES A/A</v>
+      </c>
+      <c r="N135" s="2">
+        <v>46248</v>
+      </c>
+      <c r="O135" s="8">
+        <v>1</v>
+      </c>
+      <c r="P135" t="s">
+        <v>397</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>379</v>
+      </c>
+      <c r="R135" t="s">
+        <v>381</v>
+      </c>
+      <c r="S135" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="136" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -12058,22 +13195,22 @@
         <v>893</v>
       </c>
       <c r="C136" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D136" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="E136" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>0</v>
       </c>
       <c r="G136" t="s">
         <v>314</v>
       </c>
       <c r="H136" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CPU OVATION WAYNE (POR REPARAR)</v>
       </c>
       <c r="I136" s="2">
@@ -12082,9 +13219,30 @@
       <c r="J136" s="8">
         <v>2</v>
       </c>
+      <c r="L136" t="s">
+        <v>169</v>
+      </c>
       <c r="M136" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
-        <v>NO EXISTE</v>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
+        <v>DESTORCEDORES 3/4 GASOLINA OPW</v>
+      </c>
+      <c r="N136" s="2">
+        <v>46255</v>
+      </c>
+      <c r="O136" s="8">
+        <v>2</v>
+      </c>
+      <c r="P136" t="s">
+        <v>879</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>193</v>
+      </c>
+      <c r="R136" t="s">
+        <v>381</v>
+      </c>
+      <c r="S136" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="137" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -12095,22 +13253,22 @@
         <v>894</v>
       </c>
       <c r="C137" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D137" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="E137" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>0</v>
       </c>
       <c r="G137" t="s">
         <v>315</v>
       </c>
       <c r="H137" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CPU BENNET DIESEL (POR REPARAR)</v>
       </c>
       <c r="I137" s="2">
@@ -12119,9 +13277,30 @@
       <c r="J137" s="8">
         <v>4</v>
       </c>
+      <c r="L137" t="s">
+        <v>117</v>
+      </c>
       <c r="M137" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
-        <v>NO EXISTE</v>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
+        <v>PALANCAS DE ACTIVACION PARA DIESEL WAYNE</v>
+      </c>
+      <c r="N137" s="2">
+        <v>46255</v>
+      </c>
+      <c r="O137" s="8">
+        <v>1</v>
+      </c>
+      <c r="P137" t="s">
+        <v>879</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>193</v>
+      </c>
+      <c r="R137" t="s">
+        <v>381</v>
+      </c>
+      <c r="S137" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="138" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -12132,22 +13311,22 @@
         <v>895</v>
       </c>
       <c r="C138" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D138" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="E138" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>0</v>
       </c>
       <c r="G138" t="s">
         <v>147</v>
       </c>
       <c r="H138" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>VALVULAS WAYNE SKINER HELIX W2893703-001</v>
       </c>
       <c r="I138" s="2">
@@ -12156,9 +13335,30 @@
       <c r="J138" s="8">
         <v>15</v>
       </c>
+      <c r="L138" t="s">
+        <v>100</v>
+      </c>
       <c r="M138" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
-        <v>NO EXISTE</v>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
+        <v>PISTOLA DE 3/4 P/GASOLINA</v>
+      </c>
+      <c r="N138" s="2">
+        <v>46255</v>
+      </c>
+      <c r="O138" s="8">
+        <v>1</v>
+      </c>
+      <c r="P138" t="s">
+        <v>879</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>193</v>
+      </c>
+      <c r="R138" t="s">
+        <v>381</v>
+      </c>
+      <c r="S138" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="139" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -12169,22 +13369,22 @@
         <v>896</v>
       </c>
       <c r="C139" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="D139" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>1</v>
       </c>
       <c r="E139" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>0</v>
       </c>
       <c r="G139" t="s">
         <v>145</v>
       </c>
       <c r="H139" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>VALVULAS SKINER DE DIESEL DE 2 HILOS CURVA ATLANTIC</v>
       </c>
       <c r="I139" s="2">
@@ -12193,9 +13393,30 @@
       <c r="J139" s="8">
         <v>5</v>
       </c>
+      <c r="L139" t="s">
+        <v>159</v>
+      </c>
       <c r="M139" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
-        <v>NO EXISTE</v>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
+        <v>MANGUERAS DE GASOLINA</v>
+      </c>
+      <c r="N139" s="2">
+        <v>46255</v>
+      </c>
+      <c r="O139" s="8">
+        <v>1</v>
+      </c>
+      <c r="P139" t="s">
+        <v>879</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>193</v>
+      </c>
+      <c r="R139" t="s">
+        <v>381</v>
+      </c>
+      <c r="S139" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="140" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -12206,22 +13427,22 @@
         <v>898</v>
       </c>
       <c r="C140" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>2</v>
       </c>
       <c r="D140" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>2</v>
       </c>
       <c r="E140" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>0</v>
       </c>
       <c r="G140" t="s">
         <v>316</v>
       </c>
       <c r="H140" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>BATERIA PARA RADIOS MAG ONE</v>
       </c>
       <c r="I140" s="2">
@@ -12230,9 +13451,30 @@
       <c r="J140" s="8">
         <v>1</v>
       </c>
+      <c r="L140" t="s">
+        <v>167</v>
+      </c>
       <c r="M140" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
-        <v>NO EXISTE</v>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
+        <v>FILTRO GASOLINA WAYNE 10 MICRAS</v>
+      </c>
+      <c r="N140" s="2">
+        <v>46255</v>
+      </c>
+      <c r="O140" s="8">
+        <v>3</v>
+      </c>
+      <c r="P140" t="s">
+        <v>879</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>193</v>
+      </c>
+      <c r="R140" t="s">
+        <v>381</v>
+      </c>
+      <c r="S140" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="141" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -12243,22 +13485,22 @@
         <v>899</v>
       </c>
       <c r="C141" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
         <v>16</v>
       </c>
       <c r="D141" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>12</v>
       </c>
       <c r="E141" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
         <v>4</v>
       </c>
       <c r="G141" t="s">
         <v>113</v>
       </c>
       <c r="H141" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>RADIOS MAG ONE</v>
       </c>
       <c r="I141" s="2">
@@ -12267,30 +13509,56 @@
       <c r="J141" s="8">
         <v>10</v>
       </c>
+      <c r="L141" t="s">
+        <v>168</v>
+      </c>
       <c r="M141" t="str">
-        <f>IFERROR(VLOOKUP(SALIDAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
-        <v>NO EXISTE</v>
-      </c>
-      <c r="N141" s="2"/>
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
+        <v>FILTRO DIESEL WAYNE 30 MICRAS CIMTEK</v>
+      </c>
+      <c r="N141" s="2">
+        <v>46255</v>
+      </c>
+      <c r="O141" s="8">
+        <v>2</v>
+      </c>
+      <c r="P141" t="s">
+        <v>879</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>193</v>
+      </c>
+      <c r="R141" t="s">
+        <v>381</v>
+      </c>
+      <c r="S141" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="142" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>328</v>
+      </c>
+      <c r="B142" t="s">
+        <v>1052</v>
+      </c>
       <c r="C142" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
-        <v>0</v>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
+        <v>5</v>
       </c>
       <c r="D142" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
-        <v>0</v>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
+        <v>1</v>
       </c>
       <c r="E142" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
-        <v>0</v>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
+        <v>4</v>
       </c>
       <c r="G142" t="s">
         <v>185</v>
       </c>
       <c r="H142" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">SHUT P/ AIRE </v>
       </c>
       <c r="I142" s="2">
@@ -12299,25 +13567,56 @@
       <c r="J142" s="8">
         <v>3</v>
       </c>
+      <c r="L142" t="s">
+        <v>140</v>
+      </c>
+      <c r="M142" t="str">
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
+        <v>EMPAQUES P/ CAMPANAS DE DESCARGA</v>
+      </c>
+      <c r="N142" s="2">
+        <v>46255</v>
+      </c>
+      <c r="O142" s="8">
+        <v>4</v>
+      </c>
+      <c r="P142" t="s">
+        <v>879</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>193</v>
+      </c>
+      <c r="R142" t="s">
+        <v>381</v>
+      </c>
+      <c r="S142" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="143" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>329</v>
+      </c>
+      <c r="B143" t="s">
+        <v>1053</v>
+      </c>
       <c r="C143" s="8">
-        <f>SUMIF(ENTRADAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],ENTRADAS[CANTIDAD])</f>
-        <v>0</v>
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
+        <v>5</v>
       </c>
       <c r="D143" s="8">
-        <f>SUMIF(SALIDAS[CODIGO],PRODUCTOS[[#This Row],[CODIGO]],SALIDAS[CANTIDAD])</f>
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
         <v>0</v>
       </c>
       <c r="E143" s="8">
-        <f>PRODUCTOS[[#This Row],[ENTRADAS]]-PRODUCTOS[[#This Row],[SALIDAS]]</f>
-        <v>0</v>
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
+        <v>5</v>
       </c>
       <c r="G143" t="s">
         <v>288</v>
       </c>
       <c r="H143" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>TROMPA DE COCHINO CODO DE DESCARGA</v>
       </c>
       <c r="I143" s="2">
@@ -12326,13 +13625,56 @@
       <c r="J143" s="8">
         <v>1</v>
       </c>
+      <c r="L143" t="s">
+        <v>100</v>
+      </c>
+      <c r="M143" t="str">
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
+        <v>PISTOLA DE 3/4 P/GASOLINA</v>
+      </c>
+      <c r="N143" s="2">
+        <v>46255</v>
+      </c>
+      <c r="O143" s="8">
+        <v>3</v>
+      </c>
+      <c r="P143" t="s">
+        <v>881</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>193</v>
+      </c>
+      <c r="R143" t="s">
+        <v>381</v>
+      </c>
+      <c r="S143" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="144" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>330</v>
+      </c>
+      <c r="B144" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C144" s="8">
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
+        <v>20</v>
+      </c>
+      <c r="D144" s="8">
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
+        <v>0</v>
+      </c>
+      <c r="E144" s="8">
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
+        <v>20</v>
+      </c>
       <c r="G144" t="s">
         <v>317</v>
       </c>
       <c r="H144" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CONTROL PARA DISPENSARIO WAYNE</v>
       </c>
       <c r="I144" s="2">
@@ -12341,13 +13683,50 @@
       <c r="J144" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="145" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="L144" t="s">
+        <v>328</v>
+      </c>
+      <c r="M144" t="str">
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
+        <v>CAPACITOR EMIGDIO</v>
+      </c>
+      <c r="N144" s="2">
+        <v>46244</v>
+      </c>
+      <c r="O144" s="8">
+        <v>1</v>
+      </c>
+      <c r="P144" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>1055</v>
+      </c>
+      <c r="R144" t="s">
+        <v>1056</v>
+      </c>
+      <c r="S144" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="145" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C145" s="8">
+        <f>SUMIF(ENTRADAS10[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],ENTRADAS10[CANTIDAD])</f>
+        <v>0</v>
+      </c>
+      <c r="D145" s="8">
+        <f>SUMIF(SALIDAS11[CODIGO],PRODUCTOS9[[#This Row],[CODIGO]],SALIDAS11[CANTIDAD])</f>
+        <v>0</v>
+      </c>
+      <c r="E145" s="8">
+        <f>PRODUCTOS9[[#This Row],[ENTRADAS]]-PRODUCTOS9[[#This Row],[SALIDAS]]</f>
+        <v>0</v>
+      </c>
       <c r="G145" t="s">
         <v>318</v>
       </c>
       <c r="H145" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>CHAPA PARA DISPENSARIO WAYNE</v>
       </c>
       <c r="I145" s="2">
@@ -12356,13 +13735,17 @@
       <c r="J145" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="146" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="M145" t="str">
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
+        <v>NO EXISTE</v>
+      </c>
+    </row>
+    <row r="146" spans="3:13" x14ac:dyDescent="0.2">
       <c r="G146" t="s">
         <v>319</v>
       </c>
       <c r="H146" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>REDUCCION DE CAMPANA 3/4"</v>
       </c>
       <c r="I146" s="2">
@@ -12371,13 +13754,17 @@
       <c r="J146" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="147" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="M146" t="str">
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
+        <v>NO EXISTE</v>
+      </c>
+    </row>
+    <row r="147" spans="3:13" x14ac:dyDescent="0.2">
       <c r="G147" t="s">
         <v>320</v>
       </c>
       <c r="H147" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>NIPLE ROSCA CORRIDA 3/4"</v>
       </c>
       <c r="I147" s="2">
@@ -12386,13 +13773,17 @@
       <c r="J147" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="148" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="M147" t="str">
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
+        <v>NO EXISTE</v>
+      </c>
+    </row>
+    <row r="148" spans="3:13" x14ac:dyDescent="0.2">
       <c r="G148" t="s">
         <v>321</v>
       </c>
       <c r="H148" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>FUNDA NEGRA DE 3/4"</v>
       </c>
       <c r="I148" s="2">
@@ -12401,13 +13792,17 @@
       <c r="J148" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="149" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="M148" t="str">
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
+        <v>NO EXISTE</v>
+      </c>
+    </row>
+    <row r="149" spans="3:13" x14ac:dyDescent="0.2">
       <c r="G149" t="s">
         <v>322</v>
       </c>
       <c r="H149" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERA NEGRA AGUA Y AIRE</v>
       </c>
       <c r="I149" s="2">
@@ -12416,13 +13811,17 @@
       <c r="J149" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="150" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="M149" t="str">
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
+        <v>NO EXISTE</v>
+      </c>
+    </row>
+    <row r="150" spans="3:13" x14ac:dyDescent="0.2">
       <c r="G150" t="s">
         <v>323</v>
       </c>
       <c r="H150" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>SHUT DE AIRE DISP. MECANICO</v>
       </c>
       <c r="I150" s="2">
@@ -12431,13 +13830,17 @@
       <c r="J150" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="151" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="M150" t="str">
+        <f>IFERROR(VLOOKUP(SALIDAS11[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
+        <v>NO EXISTE</v>
+      </c>
+    </row>
+    <row r="151" spans="3:13" x14ac:dyDescent="0.2">
       <c r="G151" t="s">
         <v>324</v>
       </c>
       <c r="H151" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERA LARGA DE DIESEL 6M</v>
       </c>
       <c r="I151" s="2">
@@ -12447,12 +13850,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="152" spans="3:13" x14ac:dyDescent="0.2">
       <c r="G152" t="s">
         <v>325</v>
       </c>
       <c r="H152" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>MANGUERA DE DESCARGA 6M</v>
       </c>
       <c r="I152" s="2">
@@ -12462,12 +13865,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="153" spans="3:13" x14ac:dyDescent="0.2">
       <c r="G153" t="s">
         <v>326</v>
       </c>
       <c r="H153" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v xml:space="preserve">UNIVERSAL VALVULA FLOTADORA 2 X 6 </v>
       </c>
       <c r="I153" s="2">
@@ -12477,12 +13880,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="154" spans="3:13" x14ac:dyDescent="0.2">
       <c r="G154" t="s">
         <v>288</v>
       </c>
       <c r="H154" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>TROMPA DE COCHINO CODO DE DESCARGA</v>
       </c>
       <c r="I154" s="2">
@@ -12492,12 +13895,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="155" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="155" spans="3:13" x14ac:dyDescent="0.2">
       <c r="G155" t="s">
         <v>327</v>
       </c>
       <c r="H155" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>ORING PARA VALVULA DE CORTE RAPIDO</v>
       </c>
       <c r="I155" s="2">
@@ -12507,69 +13910,99 @@
         <v>16</v>
       </c>
     </row>
-    <row r="156" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="156" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="G156" t="s">
+        <v>328</v>
+      </c>
       <c r="H156" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
-        <v>NO EXISTE</v>
-      </c>
-    </row>
-    <row r="157" spans="7:10" x14ac:dyDescent="0.2">
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
+        <v>CAPACITOR EMIGDIO</v>
+      </c>
+      <c r="I156" s="2">
+        <v>46244</v>
+      </c>
+      <c r="J156" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="157" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="G157" t="s">
+        <v>329</v>
+      </c>
       <c r="H157" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
-        <v>NO EXISTE</v>
-      </c>
-    </row>
-    <row r="158" spans="7:10" x14ac:dyDescent="0.2">
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
+        <v>CAPACITOR DON PONCHO</v>
+      </c>
+      <c r="I157" s="2">
+        <v>46244</v>
+      </c>
+      <c r="J157" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="G158" t="s">
+        <v>330</v>
+      </c>
       <c r="H158" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
-        <v>NO EXISTE</v>
-      </c>
-    </row>
-    <row r="159" spans="7:10" x14ac:dyDescent="0.2">
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
+        <v>TRAMO CORTO DE 3/4"</v>
+      </c>
+      <c r="I158" s="2">
+        <v>46255</v>
+      </c>
+      <c r="J158" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="159" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="G159" t="s">
+        <v>159</v>
+      </c>
       <c r="H159" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
-        <v>NO EXISTE</v>
-      </c>
-    </row>
-    <row r="160" spans="7:10" x14ac:dyDescent="0.2">
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
+        <v>MANGUERAS DE GASOLINA</v>
+      </c>
+      <c r="I159" s="2">
+        <v>46255</v>
+      </c>
+      <c r="J159" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="160" spans="3:13" x14ac:dyDescent="0.2">
       <c r="H160" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>NO EXISTE</v>
       </c>
     </row>
     <row r="161" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H161" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>NO EXISTE</v>
       </c>
     </row>
     <row r="162" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H162" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>NO EXISTE</v>
       </c>
     </row>
     <row r="163" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H163" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>NO EXISTE</v>
       </c>
     </row>
     <row r="164" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H164" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>NO EXISTE</v>
       </c>
     </row>
     <row r="165" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H165" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
-        <v>NO EXISTE</v>
-      </c>
-    </row>
-    <row r="166" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H166" t="str">
-        <f>IFERROR(VLOOKUP(ENTRADAS[[#This Row],[CODIGO]],PRODUCTOS[],2,FALSE),"NO EXISTE")</f>
+        <f>IFERROR(VLOOKUP(ENTRADAS10[[#This Row],[CODIGO]],PRODUCTOS9[],2,FALSE),"NO EXISTE")</f>
         <v>NO EXISTE</v>
       </c>
     </row>
@@ -18682,4 +20115,1885 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A9D0AB7-7BF0-4442-B479-36C5D7420593}">
+  <dimension ref="A1:M86"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="30.5" customWidth="1"/>
+    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" customWidth="1"/>
+    <col min="4" max="4" width="17.1640625" customWidth="1"/>
+    <col min="5" max="5" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="89.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.33203125" customWidth="1"/>
+    <col min="9" max="9" width="28.1640625" customWidth="1"/>
+    <col min="10" max="10" width="25.6640625" customWidth="1"/>
+    <col min="11" max="11" width="25.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="24" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="24" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="24" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
+        <v>907</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>908</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>909</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>910</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>911</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>912</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>913</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>914</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>915</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>916</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>917</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>918</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" s="14">
+        <v>24112600</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>920</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E8" s="15">
+        <v>2581.3092999999999</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>923</v>
+      </c>
+      <c r="G8" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" s="16" t="s">
+        <v>924</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>925</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E9" s="14">
+        <v>100.42</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>926</v>
+      </c>
+      <c r="G9" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" s="14">
+        <v>27112900</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>927</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E10" s="14">
+        <v>10.58</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>928</v>
+      </c>
+      <c r="G10" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11" s="14">
+        <v>40142000</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>929</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E11" s="14">
+        <v>30</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>930</v>
+      </c>
+      <c r="G11" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" s="14">
+        <v>40142000</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>931</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E12" s="14">
+        <v>30</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>932</v>
+      </c>
+      <c r="G12" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13" s="14">
+        <v>40142000</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>933</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E13" s="14">
+        <v>469.89</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>934</v>
+      </c>
+      <c r="G13" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14" s="14">
+        <v>26111700</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>935</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E14" s="14">
+        <v>30</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15" s="14">
+        <v>39122200</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E15" s="14">
+        <v>301.99</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16" s="14">
+        <v>40141604</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>937</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E16" s="14">
+        <v>108.12</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>938</v>
+      </c>
+      <c r="G16" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="17">
+        <v>20121445</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>939</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>922</v>
+      </c>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17" t="s">
+        <v>940</v>
+      </c>
+      <c r="G17" s="17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="17"/>
+      <c r="B18" s="17" t="s">
+        <v>941</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>922</v>
+      </c>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="17">
+        <v>16</v>
+      </c>
+      <c r="H18" s="18"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="14">
+        <v>27112502</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>942</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E19" s="14">
+        <v>99.35</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="14">
+        <v>31411800</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>943</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E20" s="14">
+        <v>208.94</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="14">
+        <v>27112502</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>944</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E21" s="14">
+        <v>39.950000000000003</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="14">
+        <v>40141604</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>945</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E22" s="14">
+        <v>96.46</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="14">
+        <v>40161513</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>946</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E23" s="14">
+        <v>12.46</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>947</v>
+      </c>
+      <c r="G23" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="14">
+        <v>40161513</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>948</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E24" s="14">
+        <v>10.82</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="14">
+        <v>40141600</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>949</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E25" s="14">
+        <v>144.81</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>950</v>
+      </c>
+      <c r="G25" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="17"/>
+      <c r="B26" s="17" t="s">
+        <v>951</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>922</v>
+      </c>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G26" s="17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="14">
+        <v>40141643</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>952</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E27" s="14">
+        <v>153.11000000000001</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A28" s="14">
+        <v>32131010</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>953</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E28" s="15">
+        <v>1493</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>954</v>
+      </c>
+      <c r="G28" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="14">
+        <v>32131010</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>955</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E29" s="15">
+        <v>1121.17</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>956</v>
+      </c>
+      <c r="G29" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="14">
+        <v>20121445</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>957</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E30" s="14">
+        <v>70.5</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G30" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="14">
+        <v>31163100</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>958</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E31" s="14">
+        <v>73.7</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="G31" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" s="14">
+        <v>40141605</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>959</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E32" s="14">
+        <v>973.7</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>960</v>
+      </c>
+      <c r="G32" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="14">
+        <v>39121408</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>961</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E33" s="14">
+        <v>197.16</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G33" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="14">
+        <v>40141600</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>962</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E34" s="14">
+        <v>363.5</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>963</v>
+      </c>
+      <c r="G34" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" s="14">
+        <v>25172411</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>964</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E35" s="14">
+        <v>454.52</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>965</v>
+      </c>
+      <c r="G35" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="14">
+        <v>31201600</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>966</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E36" s="14">
+        <v>31.06</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>967</v>
+      </c>
+      <c r="G36" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="14">
+        <v>31201600</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>968</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E37" s="14">
+        <v>8</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G37" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="14">
+        <v>31201600</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>969</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E38" s="14">
+        <v>8</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G38" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" s="14">
+        <v>11151512</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>970</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E39" s="14">
+        <v>54.6</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>971</v>
+      </c>
+      <c r="G39" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="14">
+        <v>32131010</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>972</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E40" s="14">
+        <v>285.35000000000002</v>
+      </c>
+      <c r="F40" s="14" t="s">
+        <v>973</v>
+      </c>
+      <c r="G40" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="14">
+        <v>32131010</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>974</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E41" s="14">
+        <v>53.92</v>
+      </c>
+      <c r="F41" s="14" t="s">
+        <v>975</v>
+      </c>
+      <c r="G41" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42" s="14">
+        <v>39121408</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>976</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E42" s="14">
+        <v>5</v>
+      </c>
+      <c r="F42" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="G42" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A43" s="14">
+        <v>20121445</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>977</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E43" s="14">
+        <v>44.88</v>
+      </c>
+      <c r="F43" s="19" t="s">
+        <v>978</v>
+      </c>
+      <c r="G43" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" s="14">
+        <v>27111761</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>979</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E44" s="14">
+        <v>16</v>
+      </c>
+      <c r="F44" s="14" t="s">
+        <v>980</v>
+      </c>
+      <c r="G44" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" s="14">
+        <v>24102208</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>981</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E45" s="14">
+        <v>35.75</v>
+      </c>
+      <c r="F45" s="14" t="s">
+        <v>982</v>
+      </c>
+      <c r="G45" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" s="14">
+        <v>27112900</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>983</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E46" s="14">
+        <v>18.850000000000001</v>
+      </c>
+      <c r="F46" s="14" t="s">
+        <v>984</v>
+      </c>
+      <c r="G46" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" s="17"/>
+      <c r="B47" s="17" t="s">
+        <v>985</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="D47" s="17" t="s">
+        <v>922</v>
+      </c>
+      <c r="E47" s="17"/>
+      <c r="F47" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="G47" s="17">
+        <v>16</v>
+      </c>
+      <c r="H47" s="18"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" s="14">
+        <v>31181701</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>986</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E48" s="14">
+        <v>10</v>
+      </c>
+      <c r="F48" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G48" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="14">
+        <v>26111700</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>987</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D49" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E49" s="14">
+        <v>38.58</v>
+      </c>
+      <c r="F49" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="G49" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" s="14">
+        <v>20121445</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>988</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E50" s="14">
+        <v>8.7799999999999994</v>
+      </c>
+      <c r="F50" s="14" t="s">
+        <v>989</v>
+      </c>
+      <c r="G50" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A51" s="14">
+        <v>26121600</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>990</v>
+      </c>
+      <c r="C51" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E51" s="14">
+        <v>365.62</v>
+      </c>
+      <c r="F51" s="19" t="s">
+        <v>991</v>
+      </c>
+      <c r="G51" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" s="14">
+        <v>26101113</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>992</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D52" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E52" s="14">
+        <v>1026.25</v>
+      </c>
+      <c r="F52" s="14" t="s">
+        <v>993</v>
+      </c>
+      <c r="G52" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" s="14">
+        <v>40141602</v>
+      </c>
+      <c r="B53" s="14" t="s">
+        <v>994</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E53" s="14">
+        <v>473.92</v>
+      </c>
+      <c r="F53" s="14" t="s">
+        <v>995</v>
+      </c>
+      <c r="G53" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="14">
+        <v>41111931</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>996</v>
+      </c>
+      <c r="C54" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E54" s="14">
+        <v>1620</v>
+      </c>
+      <c r="F54" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="G54" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="14">
+        <v>40141605</v>
+      </c>
+      <c r="B55" s="14" t="s">
+        <v>997</v>
+      </c>
+      <c r="C55" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D55" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E55" s="14">
+        <v>231.85</v>
+      </c>
+      <c r="F55" s="14" t="s">
+        <v>998</v>
+      </c>
+      <c r="G55" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="14">
+        <v>24122004</v>
+      </c>
+      <c r="B56" s="14" t="s">
+        <v>999</v>
+      </c>
+      <c r="C56" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D56" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E56" s="14">
+        <v>71.06</v>
+      </c>
+      <c r="F56" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="G56" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="14">
+        <v>24112600</v>
+      </c>
+      <c r="B57" s="14" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D57" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E57" s="14">
+        <v>697.5</v>
+      </c>
+      <c r="F57" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G57" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="14">
+        <v>24112600</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C58" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D58" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E58" s="14">
+        <v>978.96</v>
+      </c>
+      <c r="F58" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G58" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="17"/>
+      <c r="B59" s="17" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C59" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="D59" s="17" t="s">
+        <v>922</v>
+      </c>
+      <c r="E59" s="17"/>
+      <c r="F59" s="17" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G59" s="17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="14">
+        <v>40141734</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C60" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D60" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E60" s="14">
+        <v>595.25</v>
+      </c>
+      <c r="F60" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="G60" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="14">
+        <v>40142000</v>
+      </c>
+      <c r="B61" s="14" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C61" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D61" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E61" s="14">
+        <v>177.98</v>
+      </c>
+      <c r="F61" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G61" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" s="14">
+        <v>20121445</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C62" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D62" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E62" s="14">
+        <v>12.83</v>
+      </c>
+      <c r="F62" s="14" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G62" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" s="14">
+        <v>20121445</v>
+      </c>
+      <c r="B63" s="14" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C63" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D63" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E63" s="14">
+        <v>12.83</v>
+      </c>
+      <c r="F63" s="14" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G63" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" s="14">
+        <v>20121445</v>
+      </c>
+      <c r="B64" s="14" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C64" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D64" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E64" s="14">
+        <v>21.7</v>
+      </c>
+      <c r="F64" s="14" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G64" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65" s="14">
+        <v>40142000</v>
+      </c>
+      <c r="B65" s="14" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C65" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D65" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E65" s="14">
+        <v>2998.43</v>
+      </c>
+      <c r="F65" s="14" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G65" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" s="14">
+        <v>40142000</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C66" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D66" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E66" s="14">
+        <v>1468.77</v>
+      </c>
+      <c r="F66" s="14" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G66" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A67" s="14">
+        <v>31411904</v>
+      </c>
+      <c r="B67" s="14" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C67" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D67" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E67" s="14">
+        <v>27</v>
+      </c>
+      <c r="F67" s="14" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G67" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A68" s="14">
+        <v>31411904</v>
+      </c>
+      <c r="B68" s="14" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C68" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D68" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E68" s="14">
+        <v>25.5</v>
+      </c>
+      <c r="F68" s="14" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G68" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A69" s="14">
+        <v>31411904</v>
+      </c>
+      <c r="B69" s="14" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C69" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D69" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E69" s="14">
+        <v>46.5</v>
+      </c>
+      <c r="F69" s="14" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G69" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A70" s="14">
+        <v>31411904</v>
+      </c>
+      <c r="B70" s="14" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C70" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D70" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E70" s="14">
+        <v>23</v>
+      </c>
+      <c r="F70" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G70" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A71" s="14">
+        <v>40161513</v>
+      </c>
+      <c r="B71" s="14" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C71" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D71" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E71" s="14">
+        <v>12.46</v>
+      </c>
+      <c r="F71" s="14" t="s">
+        <v>1024</v>
+      </c>
+      <c r="G71" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A72" s="14">
+        <v>40161513</v>
+      </c>
+      <c r="B72" s="14" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C72" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D72" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E72" s="14">
+        <v>10.82</v>
+      </c>
+      <c r="F72" s="14" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G72" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A73" s="14">
+        <v>40161513</v>
+      </c>
+      <c r="B73" s="14" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C73" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D73" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E73" s="14">
+        <v>10.82</v>
+      </c>
+      <c r="F73" s="14" t="s">
+        <v>1028</v>
+      </c>
+      <c r="G73" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A74" s="14">
+        <v>40161513</v>
+      </c>
+      <c r="B74" s="14" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C74" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D74" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E74" s="14">
+        <v>12.46</v>
+      </c>
+      <c r="F74" s="14" t="s">
+        <v>1030</v>
+      </c>
+      <c r="G74" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A75" s="17"/>
+      <c r="B75" s="17" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C75" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="D75" s="17" t="s">
+        <v>922</v>
+      </c>
+      <c r="E75" s="17"/>
+      <c r="F75" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="G75" s="17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A76" s="14">
+        <v>31163100</v>
+      </c>
+      <c r="B76" s="14" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C76" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D76" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E76" s="14">
+        <v>73.7</v>
+      </c>
+      <c r="F76" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="G76" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A77" s="14">
+        <v>40142000</v>
+      </c>
+      <c r="B77" s="14" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C77" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D77" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E77" s="14">
+        <v>433.86</v>
+      </c>
+      <c r="F77" s="14" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G77" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A78" s="14">
+        <v>40142000</v>
+      </c>
+      <c r="B78" s="14" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C78" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D78" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E78" s="14">
+        <v>2113.46</v>
+      </c>
+      <c r="F78" s="14" t="s">
+        <v>1036</v>
+      </c>
+      <c r="G78" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A79" s="17">
+        <v>40142000</v>
+      </c>
+      <c r="B79" s="17" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C79" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="D79" s="17" t="s">
+        <v>922</v>
+      </c>
+      <c r="E79" s="17"/>
+      <c r="F79" s="17" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G79" s="17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80" s="17"/>
+      <c r="B80" s="17" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C80" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="D80" s="17" t="s">
+        <v>922</v>
+      </c>
+      <c r="E80" s="17"/>
+      <c r="F80" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="G80" s="17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A81" s="14">
+        <v>24112600</v>
+      </c>
+      <c r="B81" s="14" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C81" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D81" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E81" s="14">
+        <v>151.61000000000001</v>
+      </c>
+      <c r="F81" s="14" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G81" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A82" s="14">
+        <v>41111950</v>
+      </c>
+      <c r="B82" s="14" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C82" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D82" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E82" s="14">
+        <v>10287.9</v>
+      </c>
+      <c r="F82" s="14" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G82" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A83" s="14">
+        <v>25171506</v>
+      </c>
+      <c r="B83" s="14" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C83" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D83" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E83" s="14">
+        <v>16500</v>
+      </c>
+      <c r="F83" s="14" t="s">
+        <v>1045</v>
+      </c>
+      <c r="G83" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A84" s="14">
+        <v>40141600</v>
+      </c>
+      <c r="B84" s="14" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C84" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D84" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E84" s="14">
+        <v>74.06</v>
+      </c>
+      <c r="F84" s="14" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G84" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A85" s="14">
+        <v>40171700</v>
+      </c>
+      <c r="B85" s="14" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C85" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D85" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E85" s="14">
+        <v>155.04</v>
+      </c>
+      <c r="F85" s="14" t="s">
+        <v>1049</v>
+      </c>
+      <c r="G85" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A86" s="14">
+        <v>20121445</v>
+      </c>
+      <c r="B86" s="14" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C86" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D86" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="E86" s="14">
+        <v>59.9</v>
+      </c>
+      <c r="F86" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="G86" s="14">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:M86" xr:uid="{3A9D0AB7-7BF0-4442-B479-36C5D7420593}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>